--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>78738</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R2" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,26 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912889</v>
+        <v>126918815</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672798</v>
+        <v>672767</v>
       </c>
       <c r="R3" t="n">
-        <v>7091015</v>
+        <v>7090991</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,22 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918830</v>
+        <v>126912889</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672770</v>
+        <v>672798</v>
       </c>
       <c r="R4" t="n">
-        <v>7090981</v>
+        <v>7091015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,48 +958,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126912928</v>
+        <v>126918830</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672944</v>
+        <v>672770</v>
       </c>
       <c r="R5" t="n">
-        <v>7090839</v>
+        <v>7090981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,44 +1055,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126919058</v>
+        <v>126913222</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672737</v>
+        <v>672883</v>
       </c>
       <c r="R6" t="n">
-        <v>7091090</v>
+        <v>7090921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1172,32 +1172,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126913222</v>
+        <v>126912873</v>
       </c>
       <c r="B7" t="n">
-        <v>56849</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672883</v>
+        <v>672756</v>
       </c>
       <c r="R7" t="n">
-        <v>7090921</v>
+        <v>7091126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,26 +1257,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126912873</v>
+        <v>126919058</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672756</v>
+        <v>672737</v>
       </c>
       <c r="R8" t="n">
-        <v>7091126</v>
+        <v>7091090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,22 +1354,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126918821</v>
+        <v>126912932</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672752</v>
+        <v>672755</v>
       </c>
       <c r="R9" t="n">
-        <v>7091197</v>
+        <v>7091113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,26 +1455,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919053</v>
+        <v>126912715</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672698</v>
+        <v>672914</v>
       </c>
       <c r="R10" t="n">
-        <v>7091075</v>
+        <v>7090807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,26 +1552,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919056</v>
+        <v>126919053</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1607,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672702</v>
+        <v>672698</v>
       </c>
       <c r="R11" t="n">
-        <v>7091127</v>
+        <v>7091075</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912875</v>
+        <v>126919056</v>
       </c>
       <c r="B12" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1708,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672751</v>
+        <v>672702</v>
       </c>
       <c r="R12" t="n">
-        <v>7091113</v>
+        <v>7091127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,22 +1750,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912932</v>
+        <v>126912875</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,21 +1777,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1805,7 +1801,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672755</v>
+        <v>672751</v>
       </c>
       <c r="R13" t="n">
         <v>7091113</v>
@@ -1867,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126912726</v>
+        <v>126918821</v>
       </c>
       <c r="B14" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1874,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672750</v>
+        <v>672752</v>
       </c>
       <c r="R14" t="n">
-        <v>7091112</v>
+        <v>7091197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,22 +1948,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912715</v>
+        <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>79598</v>
+        <v>79600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672914</v>
+        <v>672750</v>
       </c>
       <c r="R15" t="n">
-        <v>7090807</v>
+        <v>7091112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
         <v>126918827</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R17" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B18" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R18" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
         <v>126913219</v>
       </c>
       <c r="B19" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>126918828</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>126918825</v>
       </c>
       <c r="B21" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>78647</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R22" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R23" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>126913216</v>
       </c>
       <c r="B24" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>126919059</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>126912870</v>
       </c>
       <c r="B26" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>126912860</v>
       </c>
       <c r="B27" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126918831</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912749</v>
+        <v>126912933</v>
       </c>
       <c r="B29" t="n">
-        <v>92727</v>
+        <v>78678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672946</v>
+        <v>672871</v>
       </c>
       <c r="R29" t="n">
-        <v>7090821</v>
+        <v>7090905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912933</v>
+        <v>126912749</v>
       </c>
       <c r="B30" t="n">
-        <v>78647</v>
+        <v>92802</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672871</v>
+        <v>672946</v>
       </c>
       <c r="R30" t="n">
-        <v>7090905</v>
+        <v>7090821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
         <v>126912717</v>
       </c>
       <c r="B31" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>126912944</v>
       </c>
       <c r="B32" t="n">
-        <v>78386</v>
+        <v>78417</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>126918824</v>
       </c>
       <c r="B33" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
         <v>126912776</v>
       </c>
       <c r="B34" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3944,7 +3944,7 @@
         <v>126912716</v>
       </c>
       <c r="B35" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919051</v>
+        <v>126919054</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672702</v>
+        <v>672705</v>
       </c>
       <c r="R36" t="n">
-        <v>7091061</v>
+        <v>7091127</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919054</v>
+        <v>126919057</v>
       </c>
       <c r="B37" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672705</v>
+        <v>672730</v>
       </c>
       <c r="R37" t="n">
-        <v>7091127</v>
+        <v>7091091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126918826</v>
+        <v>126912877</v>
       </c>
       <c r="B38" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672744</v>
+        <v>672754</v>
       </c>
       <c r="R38" t="n">
-        <v>7091079</v>
+        <v>7091099</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,26 +4325,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912877</v>
+        <v>126918826</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4376,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672754</v>
+        <v>672744</v>
       </c>
       <c r="R39" t="n">
-        <v>7091099</v>
+        <v>7091079</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4426,22 +4422,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
         <v>126912774</v>
       </c>
       <c r="B40" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4528,17 +4528,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919057</v>
+        <v>126919051</v>
       </c>
       <c r="B41" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672730</v>
+        <v>672702</v>
       </c>
       <c r="R41" t="n">
-        <v>7091091</v>
+        <v>7091061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4639,7 +4639,7 @@
         <v>126912927</v>
       </c>
       <c r="B42" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,17 +4726,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126913218</v>
+        <v>126918820</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672656</v>
+        <v>672755</v>
       </c>
       <c r="R43" t="n">
-        <v>7091011</v>
+        <v>7091121</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,12 +4818,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4834,10 +4834,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126918820</v>
+        <v>126912887</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672755</v>
+        <v>672750</v>
       </c>
       <c r="R44" t="n">
-        <v>7091121</v>
+        <v>7091052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,26 +4919,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912887</v>
+        <v>126913218</v>
       </c>
       <c r="B45" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4970,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672750</v>
+        <v>672656</v>
       </c>
       <c r="R45" t="n">
-        <v>7091052</v>
+        <v>7091011</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5020,22 +5016,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>126912865</v>
       </c>
       <c r="B46" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>126919050</v>
       </c>
       <c r="B48" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B49" t="n">
-        <v>92535</v>
+        <v>91337</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,48 +5416,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B50" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R50" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,22 +5513,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R51" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5614,26 +5614,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912762</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>91263</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5637,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672743</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7091094</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,22 +5711,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>126912718</v>
       </c>
       <c r="B53" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912723</v>
+        <v>126913223</v>
       </c>
       <c r="B54" t="n">
-        <v>91167</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672755</v>
+        <v>672862</v>
       </c>
       <c r="R54" t="n">
-        <v>7091097</v>
+        <v>7090889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,22 +5909,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913223</v>
+        <v>126919060</v>
       </c>
       <c r="B55" t="n">
-        <v>79012</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,21 +5936,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672862</v>
+        <v>672791</v>
       </c>
       <c r="R55" t="n">
-        <v>7090889</v>
+        <v>7091150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,12 +6010,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6025,7 +6029,7 @@
         <v>126912868</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6122,7 +6126,7 @@
         <v>126912879</v>
       </c>
       <c r="B57" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6216,32 +6220,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919018</v>
+        <v>126912723</v>
       </c>
       <c r="B58" t="n">
-        <v>56849</v>
+        <v>91241</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6251,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672883</v>
+        <v>672755</v>
       </c>
       <c r="R58" t="n">
-        <v>7090877</v>
+        <v>7091097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6289,11 +6293,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6306,48 +6305,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919060</v>
+        <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>78980</v>
+        <v>56849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6352,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672791</v>
+        <v>672883</v>
       </c>
       <c r="R59" t="n">
-        <v>7091150</v>
+        <v>7090877</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6393,6 +6388,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912884</v>
+        <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>78980</v>
+        <v>78678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672746</v>
+        <v>672873</v>
       </c>
       <c r="R60" t="n">
-        <v>7091051</v>
+        <v>7090916</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,17 +6513,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126912892</v>
       </c>
       <c r="B61" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672787</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7090995</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,26 +6605,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912892</v>
+        <v>126912884</v>
       </c>
       <c r="B62" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6656,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672787</v>
+        <v>672746</v>
       </c>
       <c r="R62" t="n">
-        <v>7090995</v>
+        <v>7091051</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6718,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912934</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>78647</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672873</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7090916</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,22 +6799,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126917430</v>
       </c>
       <c r="B64" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>126917438</v>
       </c>
       <c r="B65" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126917439</v>
       </c>
       <c r="B66" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>126917436</v>
       </c>
       <c r="B69" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>126917440</v>
       </c>
       <c r="B70" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>57817</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,31 +7571,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7647,6 +7642,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7669,10 +7665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>78980</v>
+        <v>57817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7680,26 +7676,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7707,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R72" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7751,7 +7752,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>126917444</v>
       </c>
       <c r="B73" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>126917442</v>
       </c>
       <c r="B74" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>78980</v>
+        <v>91580</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R75" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>91506</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R76" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8307,7 +8307,7 @@
         <v>126913591</v>
       </c>
       <c r="B78" t="n">
-        <v>78647</v>
+        <v>78678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8610,7 +8610,7 @@
         <v>126913586</v>
       </c>
       <c r="B81" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>126913587</v>
       </c>
       <c r="B82" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>126913589</v>
       </c>
       <c r="B83" t="n">
-        <v>79004</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>126913584</v>
       </c>
       <c r="B86" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>126913585</v>
       </c>
       <c r="B87" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>126913593</v>
       </c>
       <c r="B88" t="n">
-        <v>79012</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,17 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918815</v>
+        <v>126912889</v>
       </c>
       <c r="B3" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672767</v>
+        <v>672798</v>
       </c>
       <c r="R3" t="n">
-        <v>7090991</v>
+        <v>7091015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,26 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126912889</v>
+        <v>126918830</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672798</v>
+        <v>672770</v>
       </c>
       <c r="R4" t="n">
-        <v>7091015</v>
+        <v>7090981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,22 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918830</v>
+        <v>126918815</v>
       </c>
       <c r="B5" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672770</v>
+        <v>672767</v>
       </c>
       <c r="R5" t="n">
-        <v>7090981</v>
+        <v>7090991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1175,7 +1175,7 @@
         <v>126912873</v>
       </c>
       <c r="B7" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>126919058</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912932</v>
+        <v>126919056</v>
       </c>
       <c r="B9" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672755</v>
+        <v>672702</v>
       </c>
       <c r="R9" t="n">
-        <v>7091113</v>
+        <v>7091127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,22 +1455,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912715</v>
+        <v>126912875</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672914</v>
+        <v>672751</v>
       </c>
       <c r="R10" t="n">
-        <v>7090807</v>
+        <v>7091113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919053</v>
+        <v>126918821</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672698</v>
+        <v>672752</v>
       </c>
       <c r="R11" t="n">
-        <v>7091075</v>
+        <v>7091197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1653,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1665,10 +1669,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919056</v>
+        <v>126912715</v>
       </c>
       <c r="B12" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1680,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672702</v>
+        <v>672914</v>
       </c>
       <c r="R12" t="n">
-        <v>7091127</v>
+        <v>7090807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,26 +1754,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912875</v>
+        <v>126919053</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672751</v>
+        <v>672698</v>
       </c>
       <c r="R13" t="n">
-        <v>7091113</v>
+        <v>7091075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,22 +1851,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918821</v>
+        <v>126912726</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,21 +1878,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672752</v>
+        <v>672750</v>
       </c>
       <c r="R14" t="n">
-        <v>7091197</v>
+        <v>7091112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,26 +1952,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912726</v>
+        <v>126912932</v>
       </c>
       <c r="B15" t="n">
-        <v>79600</v>
+        <v>78681</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672750</v>
+        <v>672755</v>
       </c>
       <c r="R15" t="n">
-        <v>7091112</v>
+        <v>7091113</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2064,7 +2064,7 @@
         <v>126918827</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>126912935</v>
       </c>
       <c r="B18" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
         <v>126913219</v>
       </c>
       <c r="B19" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
         <v>126918828</v>
       </c>
       <c r="B20" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>126918825</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>126913216</v>
       </c>
       <c r="B24" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>126919059</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>126912870</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>126912860</v>
       </c>
       <c r="B27" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126918831</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912933</v>
+        <v>126912749</v>
       </c>
       <c r="B29" t="n">
-        <v>78678</v>
+        <v>92808</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672871</v>
+        <v>672946</v>
       </c>
       <c r="R29" t="n">
-        <v>7090905</v>
+        <v>7090821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912749</v>
+        <v>126912933</v>
       </c>
       <c r="B30" t="n">
-        <v>92802</v>
+        <v>78681</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672946</v>
+        <v>672871</v>
       </c>
       <c r="R30" t="n">
-        <v>7090821</v>
+        <v>7090905</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3547,7 +3547,7 @@
         <v>126912717</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>126912944</v>
       </c>
       <c r="B32" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>126918824</v>
       </c>
       <c r="B33" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R34" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3934,17 +3934,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B35" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R35" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
         <v>126919054</v>
       </c>
       <c r="B36" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>126919057</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>126912877</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>126918826</v>
       </c>
       <c r="B39" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4438,10 +4438,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R40" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,22 +4523,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919051</v>
+        <v>126912774</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672702</v>
+        <v>672889</v>
       </c>
       <c r="R41" t="n">
-        <v>7091061</v>
+        <v>7090793</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,48 +4624,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912927</v>
+        <v>126919016</v>
       </c>
       <c r="B42" t="n">
-        <v>92609</v>
+        <v>57479</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>102976</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672768</v>
+        <v>672887</v>
       </c>
       <c r="R42" t="n">
-        <v>7091045</v>
+        <v>7090802</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,44 +4721,48 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126918820</v>
+        <v>126912927</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>92615</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4768,10 +4772,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672755</v>
+        <v>672768</v>
       </c>
       <c r="R43" t="n">
-        <v>7091121</v>
+        <v>7091045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,26 +4822,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912887</v>
+        <v>126918820</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672750</v>
+        <v>672755</v>
       </c>
       <c r="R44" t="n">
-        <v>7091052</v>
+        <v>7091121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,22 +4919,26 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913218</v>
+        <v>126912887</v>
       </c>
       <c r="B45" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4966,10 +4970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672656</v>
+        <v>672750</v>
       </c>
       <c r="R45" t="n">
-        <v>7091011</v>
+        <v>7091052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5016,26 +5020,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912865</v>
+        <v>126913218</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672783</v>
+        <v>672656</v>
       </c>
       <c r="R46" t="n">
-        <v>7091147</v>
+        <v>7091011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,44 +5117,48 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919016</v>
+        <v>126912865</v>
       </c>
       <c r="B47" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5164,10 +5168,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672887</v>
+        <v>672783</v>
       </c>
       <c r="R47" t="n">
-        <v>7090802</v>
+        <v>7091147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,26 +5218,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>126919050</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126912762</v>
       </c>
       <c r="B49" t="n">
-        <v>91337</v>
+        <v>91343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5431,7 +5431,7 @@
         <v>126919079</v>
       </c>
       <c r="B50" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5532,7 +5532,7 @@
         <v>126912713</v>
       </c>
       <c r="B51" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>126912718</v>
       </c>
       <c r="B53" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,32 +5824,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913223</v>
+        <v>126919018</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>56849</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672862</v>
+        <v>672883</v>
       </c>
       <c r="R54" t="n">
-        <v>7090889</v>
+        <v>7090877</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5897,6 +5897,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5909,12 +5914,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5928,7 +5933,7 @@
         <v>126919060</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6029,7 +6034,7 @@
         <v>126912868</v>
       </c>
       <c r="B56" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6123,10 +6128,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912879</v>
+        <v>126912723</v>
       </c>
       <c r="B57" t="n">
-        <v>79011</v>
+        <v>91247</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6139,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6163,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672751</v>
+        <v>672755</v>
       </c>
       <c r="R57" t="n">
-        <v>7091095</v>
+        <v>7091097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6220,10 +6225,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912723</v>
+        <v>126913223</v>
       </c>
       <c r="B58" t="n">
-        <v>91241</v>
+        <v>79046</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,21 +6236,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672755</v>
+        <v>672862</v>
       </c>
       <c r="R58" t="n">
-        <v>7091097</v>
+        <v>7090889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6305,44 +6310,48 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919018</v>
+        <v>126912879</v>
       </c>
       <c r="B59" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6352,10 +6361,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>672751</v>
       </c>
       <c r="R59" t="n">
-        <v>7090877</v>
+        <v>7091095</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6390,11 +6399,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6407,26 +6411,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
         <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,17 +6513,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912892</v>
+        <v>126913217</v>
       </c>
       <c r="B61" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672787</v>
+        <v>672643</v>
       </c>
       <c r="R61" t="n">
-        <v>7090995</v>
+        <v>7091013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,22 +6605,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912884</v>
+        <v>126912892</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6652,10 +6656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672746</v>
+        <v>672787</v>
       </c>
       <c r="R62" t="n">
-        <v>7091051</v>
+        <v>7090995</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126913217</v>
+        <v>126912884</v>
       </c>
       <c r="B63" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672643</v>
+        <v>672746</v>
       </c>
       <c r="R63" t="n">
-        <v>7091013</v>
+        <v>7091051</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6799,26 +6803,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126917430</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>126917438</v>
       </c>
       <c r="B65" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126917439</v>
       </c>
       <c r="B66" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7135,37 +7135,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B67" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7173,10 +7174,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R67" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7211,13 +7212,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7240,38 +7245,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B68" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7279,10 +7283,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R68" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7317,17 +7321,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>126917436</v>
       </c>
       <c r="B69" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>126917440</v>
       </c>
       <c r="B70" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B71" t="n">
-        <v>79011</v>
+        <v>57817</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,26 +7571,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7598,10 +7603,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R71" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7642,7 +7647,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7665,10 +7669,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B72" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7676,31 +7680,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7708,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R72" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7752,6 +7751,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>126917444</v>
       </c>
       <c r="B73" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>126917442</v>
       </c>
       <c r="B74" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B75" t="n">
-        <v>91580</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R75" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B76" t="n">
-        <v>79011</v>
+        <v>91586</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R76" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8307,7 +8307,7 @@
         <v>126913591</v>
       </c>
       <c r="B78" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>126913586</v>
       </c>
       <c r="B81" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>126913587</v>
       </c>
       <c r="B82" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>126913589</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>126913584</v>
       </c>
       <c r="B86" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>126913585</v>
       </c>
       <c r="B87" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>126913593</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912928</v>
+        <v>126912889</v>
       </c>
       <c r="B2" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672944</v>
+        <v>672798</v>
       </c>
       <c r="R2" t="n">
-        <v>7090839</v>
+        <v>7091015</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912889</v>
+        <v>126912928</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672798</v>
+        <v>672944</v>
       </c>
       <c r="R3" t="n">
-        <v>7091015</v>
+        <v>7090839</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918830</v>
+        <v>126918815</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672770</v>
+        <v>672767</v>
       </c>
       <c r="R4" t="n">
-        <v>7090981</v>
+        <v>7090991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918815</v>
+        <v>126918830</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672767</v>
+        <v>672770</v>
       </c>
       <c r="R5" t="n">
-        <v>7090991</v>
+        <v>7090981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126913222</v>
+        <v>126912873</v>
       </c>
       <c r="B6" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672883</v>
+        <v>672756</v>
       </c>
       <c r="R6" t="n">
-        <v>7090921</v>
+        <v>7091126</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,23 +1156,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126912873</v>
+        <v>126919058</v>
       </c>
       <c r="B7" t="n">
         <v>79014</v>
@@ -1207,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672756</v>
+        <v>672737</v>
       </c>
       <c r="R7" t="n">
-        <v>7091126</v>
+        <v>7091090</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,44 +1253,48 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126919058</v>
+        <v>126913222</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672737</v>
+        <v>672883</v>
       </c>
       <c r="R8" t="n">
-        <v>7091090</v>
+        <v>7090921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,12 +1354,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919056</v>
+        <v>126919053</v>
       </c>
       <c r="B9" t="n">
         <v>79014</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672702</v>
+        <v>672698</v>
       </c>
       <c r="R9" t="n">
-        <v>7091127</v>
+        <v>7091075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126919056</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672702</v>
       </c>
       <c r="R10" t="n">
-        <v>7091113</v>
+        <v>7091127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,19 +1556,23 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126912875</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1603,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672751</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7091113</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,26 +1657,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912715</v>
+        <v>126912932</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,21 +1680,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672914</v>
+        <v>672755</v>
       </c>
       <c r="R12" t="n">
-        <v>7090807</v>
+        <v>7091113</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919053</v>
+        <v>126912715</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672698</v>
+        <v>672914</v>
       </c>
       <c r="R13" t="n">
-        <v>7091075</v>
+        <v>7090807</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,26 +1851,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126912726</v>
+        <v>126918821</v>
       </c>
       <c r="B14" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1874,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672750</v>
+        <v>672752</v>
       </c>
       <c r="R14" t="n">
-        <v>7091112</v>
+        <v>7091197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,22 +1948,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912932</v>
+        <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>78681</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672755</v>
+        <v>672750</v>
       </c>
       <c r="R15" t="n">
-        <v>7091113</v>
+        <v>7091112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,14 +2054,14 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918827</v>
+        <v>126912882</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672753</v>
+        <v>672738</v>
       </c>
       <c r="R16" t="n">
-        <v>7091016</v>
+        <v>7091066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,26 +2146,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2173,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R17" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2259,10 +2255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912935</v>
+        <v>126918827</v>
       </c>
       <c r="B18" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2266,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672815</v>
+        <v>672753</v>
       </c>
       <c r="R18" t="n">
-        <v>7090911</v>
+        <v>7091016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,15 +2340,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912933</v>
+        <v>126912717</v>
       </c>
       <c r="B30" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672871</v>
+        <v>672735</v>
       </c>
       <c r="R30" t="n">
-        <v>7090905</v>
+        <v>7091083</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912717</v>
+        <v>126912944</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>78420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672735</v>
+        <v>672756</v>
       </c>
       <c r="R31" t="n">
-        <v>7091083</v>
+        <v>7091093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,6 +3615,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3641,10 +3646,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912944</v>
+        <v>126912933</v>
       </c>
       <c r="B32" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,21 +3657,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3676,10 +3681,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672756</v>
+        <v>672871</v>
       </c>
       <c r="R32" t="n">
-        <v>7091093</v>
+        <v>7090905</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,11 +3717,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B34" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R34" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R35" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912877</v>
+        <v>126912774</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672754</v>
+        <v>672889</v>
       </c>
       <c r="R38" t="n">
-        <v>7091099</v>
+        <v>7090793</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126918826</v>
+        <v>126912877</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672744</v>
+        <v>672754</v>
       </c>
       <c r="R39" t="n">
-        <v>7091079</v>
+        <v>7091099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,23 +4422,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919051</v>
+        <v>126918826</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4473,10 +4469,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672702</v>
+        <v>672744</v>
       </c>
       <c r="R40" t="n">
-        <v>7091061</v>
+        <v>7091079</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,12 +4519,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4539,7 +4535,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4574,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R41" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4624,44 +4620,48 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126919016</v>
+        <v>126913218</v>
       </c>
       <c r="B42" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672887</v>
+        <v>672656</v>
       </c>
       <c r="R42" t="n">
-        <v>7090802</v>
+        <v>7091011</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,12 +4721,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
@@ -4737,32 +4737,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912927</v>
+        <v>126912865</v>
       </c>
       <c r="B43" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4772,10 +4772,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672768</v>
+        <v>672783</v>
       </c>
       <c r="R43" t="n">
-        <v>7091045</v>
+        <v>7091147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4834,32 +4834,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126918820</v>
+        <v>126912927</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672755</v>
+        <v>672768</v>
       </c>
       <c r="R44" t="n">
-        <v>7091121</v>
+        <v>7091045</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,23 +4919,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912887</v>
+        <v>126918820</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -4970,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672750</v>
+        <v>672755</v>
       </c>
       <c r="R45" t="n">
-        <v>7091052</v>
+        <v>7091121</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5020,19 +5016,23 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913218</v>
+        <v>126912887</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672656</v>
+        <v>672750</v>
       </c>
       <c r="R46" t="n">
-        <v>7091011</v>
+        <v>7091052</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,48 +5117,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912865</v>
+        <v>126919016</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5168,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672783</v>
+        <v>672887</v>
       </c>
       <c r="R47" t="n">
-        <v>7091147</v>
+        <v>7090802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,15 +5214,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5331,10 +5331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B49" t="n">
-        <v>91343</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,21 +5342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R49" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5421,39 +5421,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919079</v>
+        <v>126919049</v>
       </c>
       <c r="B50" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672953</v>
+        <v>672651</v>
       </c>
       <c r="R50" t="n">
-        <v>7090819</v>
+        <v>7091012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912713</v>
+        <v>126912762</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>91343</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672780</v>
+        <v>672743</v>
       </c>
       <c r="R51" t="n">
-        <v>7091043</v>
+        <v>7091094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,32 +5626,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126919079</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672953</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7090819</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5817,39 +5817,39 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126919018</v>
+        <v>126913223</v>
       </c>
       <c r="B54" t="n">
-        <v>56849</v>
+        <v>79046</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672883</v>
+        <v>672862</v>
       </c>
       <c r="R54" t="n">
-        <v>7090877</v>
+        <v>7090889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5897,11 +5897,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5914,12 +5909,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
@@ -5930,10 +5925,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919060</v>
+        <v>126912723</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>91247</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5941,21 +5936,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5965,10 +5960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672791</v>
+        <v>672755</v>
       </c>
       <c r="R55" t="n">
-        <v>7091150</v>
+        <v>7091097</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6015,23 +6010,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912868</v>
+        <v>126919060</v>
       </c>
       <c r="B56" t="n">
         <v>79014</v>
@@ -6066,10 +6057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672779</v>
+        <v>672791</v>
       </c>
       <c r="R56" t="n">
-        <v>7091147</v>
+        <v>7091150</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6116,44 +6107,48 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912723</v>
+        <v>126919018</v>
       </c>
       <c r="B57" t="n">
-        <v>91247</v>
+        <v>56849</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6163,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672755</v>
+        <v>672883</v>
       </c>
       <c r="R57" t="n">
-        <v>7091097</v>
+        <v>7090877</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6201,6 +6196,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6213,22 +6213,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126913223</v>
+        <v>126912868</v>
       </c>
       <c r="B58" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,21 +6240,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6264,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672862</v>
+        <v>672779</v>
       </c>
       <c r="R58" t="n">
-        <v>7090889</v>
+        <v>7091147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,19 +6314,15 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912934</v>
+        <v>126912884</v>
       </c>
       <c r="B60" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672873</v>
+        <v>672746</v>
       </c>
       <c r="R60" t="n">
-        <v>7090916</v>
+        <v>7091051</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6718,10 +6718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912884</v>
+        <v>126912934</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672746</v>
+        <v>672873</v>
       </c>
       <c r="R63" t="n">
-        <v>7091051</v>
+        <v>7090916</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,31 +7571,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7647,6 +7642,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7669,10 +7665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7680,26 +7676,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7707,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R72" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7751,7 +7752,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91586</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R75" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>91586</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R76" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R79" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R80" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B84" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R84" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R85" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -2356,7 +2356,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126913219</v>
+        <v>126918828</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672627</v>
+        <v>672757</v>
       </c>
       <c r="R19" t="n">
-        <v>7091008</v>
+        <v>7091027</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,12 +2441,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2457,7 +2457,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918828</v>
+        <v>126918825</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672757</v>
+        <v>672764</v>
       </c>
       <c r="R20" t="n">
-        <v>7091027</v>
+        <v>7091153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918825</v>
+        <v>126913219</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672764</v>
+        <v>672627</v>
       </c>
       <c r="R21" t="n">
-        <v>7091153</v>
+        <v>7091008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,12 +2643,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -5331,10 +5331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912713</v>
+        <v>126912762</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>91343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,21 +5342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672780</v>
+        <v>672743</v>
       </c>
       <c r="R49" t="n">
-        <v>7091043</v>
+        <v>7091094</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5421,39 +5421,39 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919049</v>
+        <v>126919079</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>92615</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672651</v>
+        <v>672953</v>
       </c>
       <c r="R50" t="n">
-        <v>7091012</v>
+        <v>7090819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5529,10 +5529,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B51" t="n">
-        <v>91343</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5619,39 +5619,39 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919079</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672953</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7090819</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912884</v>
+        <v>126912892</v>
       </c>
       <c r="B60" t="n">
         <v>79014</v>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672746</v>
+        <v>672787</v>
       </c>
       <c r="R60" t="n">
-        <v>7091051</v>
+        <v>7090995</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126912934</v>
       </c>
       <c r="B61" t="n">
-        <v>79632</v>
+        <v>78681</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672873</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7090916</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,23 +6605,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912892</v>
+        <v>126912884</v>
       </c>
       <c r="B62" t="n">
         <v>79014</v>
@@ -6656,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672787</v>
+        <v>672746</v>
       </c>
       <c r="R62" t="n">
-        <v>7090995</v>
+        <v>7091051</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6718,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912934</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672873</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7090916</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,15 +6799,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7135,38 +7135,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7174,10 +7173,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R67" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7212,17 +7211,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7245,37 +7240,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7283,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R68" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7321,13 +7317,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R84" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R85" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912889</v>
+        <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672798</v>
+        <v>672944</v>
       </c>
       <c r="R2" t="n">
-        <v>7091015</v>
+        <v>7090839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -765,39 +765,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912928</v>
+        <v>126912889</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672944</v>
+        <v>672798</v>
       </c>
       <c r="R3" t="n">
-        <v>7090839</v>
+        <v>7091015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918815</v>
+        <v>126918830</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672767</v>
+        <v>672770</v>
       </c>
       <c r="R4" t="n">
-        <v>7090991</v>
+        <v>7090981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918830</v>
+        <v>126918815</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672770</v>
+        <v>672767</v>
       </c>
       <c r="R5" t="n">
-        <v>7090981</v>
+        <v>7090991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919053</v>
+        <v>126912932</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672698</v>
+        <v>672755</v>
       </c>
       <c r="R9" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,23 +1455,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919056</v>
+        <v>126912875</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1506,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672702</v>
+        <v>672751</v>
       </c>
       <c r="R10" t="n">
-        <v>7091127</v>
+        <v>7091113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,23 +1552,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126912875</v>
+        <v>126918821</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1607,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672751</v>
+        <v>672752</v>
       </c>
       <c r="R11" t="n">
-        <v>7091113</v>
+        <v>7091197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,22 +1649,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912932</v>
+        <v>126912715</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672755</v>
+        <v>672914</v>
       </c>
       <c r="R12" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912715</v>
+        <v>126912726</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>79603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672914</v>
+        <v>672750</v>
       </c>
       <c r="R13" t="n">
-        <v>7090807</v>
+        <v>7091112</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1856,14 +1852,14 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918821</v>
+        <v>126919053</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -1898,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672752</v>
+        <v>672698</v>
       </c>
       <c r="R14" t="n">
-        <v>7091197</v>
+        <v>7091075</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,12 +1944,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1964,10 +1960,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912726</v>
+        <v>126919056</v>
       </c>
       <c r="B15" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1971,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672750</v>
+        <v>672702</v>
       </c>
       <c r="R15" t="n">
-        <v>7091112</v>
+        <v>7091127</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,22 +2045,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R16" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,17 +2151,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R17" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918828</v>
+        <v>126913219</v>
       </c>
       <c r="B19" t="n">
         <v>79014</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672757</v>
+        <v>672627</v>
       </c>
       <c r="R19" t="n">
-        <v>7091027</v>
+        <v>7091008</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,12 +2441,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2457,7 +2457,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918825</v>
+        <v>126918828</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672764</v>
+        <v>672757</v>
       </c>
       <c r="R20" t="n">
-        <v>7091153</v>
+        <v>7091027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126913219</v>
+        <v>126918825</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672627</v>
+        <v>672764</v>
       </c>
       <c r="R21" t="n">
-        <v>7091008</v>
+        <v>7091153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,12 +2643,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R22" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R23" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,7 +2853,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126913216</v>
+        <v>126919059</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672804</v>
+        <v>672732</v>
       </c>
       <c r="R24" t="n">
-        <v>7091051</v>
+        <v>7091173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,12 +2938,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2954,7 +2954,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126919059</v>
+        <v>126913216</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672732</v>
+        <v>672804</v>
       </c>
       <c r="R25" t="n">
-        <v>7091173</v>
+        <v>7091051</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,12 +3039,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912749</v>
+        <v>126912933</v>
       </c>
       <c r="B29" t="n">
-        <v>92808</v>
+        <v>78681</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672946</v>
+        <v>672871</v>
       </c>
       <c r="R29" t="n">
-        <v>7090821</v>
+        <v>7090905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912717</v>
+        <v>126912749</v>
       </c>
       <c r="B30" t="n">
-        <v>79632</v>
+        <v>92809</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672735</v>
+        <v>672946</v>
       </c>
       <c r="R30" t="n">
-        <v>7091083</v>
+        <v>7090821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3537,17 +3537,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912944</v>
+        <v>126912717</v>
       </c>
       <c r="B31" t="n">
-        <v>78420</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672756</v>
+        <v>672735</v>
       </c>
       <c r="R31" t="n">
-        <v>7091093</v>
+        <v>7091083</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,11 +3615,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,10 +3641,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912933</v>
+        <v>126912944</v>
       </c>
       <c r="B32" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3657,21 +3652,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3681,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672871</v>
+        <v>672756</v>
       </c>
       <c r="R32" t="n">
-        <v>7090905</v>
+        <v>7091093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,6 +3712,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919054</v>
+        <v>126919057</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672705</v>
+        <v>672730</v>
       </c>
       <c r="R36" t="n">
-        <v>7091127</v>
+        <v>7091091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919057</v>
+        <v>126912877</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672730</v>
+        <v>672754</v>
       </c>
       <c r="R37" t="n">
-        <v>7091091</v>
+        <v>7091099</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,19 +4224,15 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4337,7 +4333,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912877</v>
+        <v>126919051</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4372,10 +4368,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672754</v>
+        <v>672702</v>
       </c>
       <c r="R39" t="n">
-        <v>7091099</v>
+        <v>7091061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,19 +4418,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918826</v>
+        <v>126919054</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4469,10 +4469,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672744</v>
+        <v>672705</v>
       </c>
       <c r="R40" t="n">
-        <v>7091079</v>
+        <v>7091127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4519,12 +4519,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4535,7 +4535,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919051</v>
+        <v>126918826</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672702</v>
+        <v>672744</v>
       </c>
       <c r="R41" t="n">
-        <v>7091061</v>
+        <v>7091079</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,12 +4620,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
@@ -4636,32 +4636,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126913218</v>
+        <v>126912927</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672656</v>
+        <v>672768</v>
       </c>
       <c r="R42" t="n">
-        <v>7091011</v>
+        <v>7091045</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,23 +4721,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912865</v>
+        <v>126912887</v>
       </c>
       <c r="B43" t="n">
         <v>79014</v>
@@ -4772,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672783</v>
+        <v>672750</v>
       </c>
       <c r="R43" t="n">
-        <v>7091147</v>
+        <v>7091052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4834,32 +4830,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912927</v>
+        <v>126912865</v>
       </c>
       <c r="B44" t="n">
-        <v>92615</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4869,10 +4865,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672768</v>
+        <v>672783</v>
       </c>
       <c r="R44" t="n">
-        <v>7091045</v>
+        <v>7091147</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5032,7 +5028,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912887</v>
+        <v>126913218</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5067,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672750</v>
+        <v>672656</v>
       </c>
       <c r="R46" t="n">
-        <v>7091052</v>
+        <v>7091011</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,15 +5113,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5331,10 +5331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912762</v>
+        <v>126919049</v>
       </c>
       <c r="B49" t="n">
-        <v>91343</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,21 +5342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672743</v>
+        <v>672651</v>
       </c>
       <c r="R49" t="n">
-        <v>7091094</v>
+        <v>7091012</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,44 +5416,48 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B50" t="n">
-        <v>92615</v>
+        <v>91344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R50" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5513,48 +5517,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R51" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5614,22 +5614,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5711,19 +5715,15 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5928,7 +5928,7 @@
         <v>126912723</v>
       </c>
       <c r="B55" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6423,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912892</v>
+        <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672787</v>
+        <v>672873</v>
       </c>
       <c r="R60" t="n">
-        <v>7090995</v>
+        <v>7090916</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,17 +6513,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912934</v>
+        <v>126912884</v>
       </c>
       <c r="B61" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672873</v>
+        <v>672746</v>
       </c>
       <c r="R61" t="n">
-        <v>7090916</v>
+        <v>7091051</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912884</v>
+        <v>126913217</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672746</v>
+        <v>672643</v>
       </c>
       <c r="R62" t="n">
-        <v>7091051</v>
+        <v>7091013</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,22 +6702,26 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126913217</v>
+        <v>126912892</v>
       </c>
       <c r="B63" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672643</v>
+        <v>672787</v>
       </c>
       <c r="R63" t="n">
-        <v>7091013</v>
+        <v>7090995</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6799,19 +6803,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7987,7 +7987,7 @@
         <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912889</v>
+        <v>126918830</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672798</v>
+        <v>672770</v>
       </c>
       <c r="R3" t="n">
-        <v>7091015</v>
+        <v>7090981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918830</v>
+        <v>126918815</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672770</v>
+        <v>672767</v>
       </c>
       <c r="R4" t="n">
-        <v>7090981</v>
+        <v>7090991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -970,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918815</v>
+        <v>126912889</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672767</v>
+        <v>672798</v>
       </c>
       <c r="R5" t="n">
-        <v>7090991</v>
+        <v>7091015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,19 +1059,15 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1467,7 +1467,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126919053</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672698</v>
       </c>
       <c r="R10" t="n">
-        <v>7091113</v>
+        <v>7091075</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,19 +1552,23 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126919056</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1599,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672702</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7091127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1653,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1859,7 +1863,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919053</v>
+        <v>126912875</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -1894,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672698</v>
+        <v>672751</v>
       </c>
       <c r="R14" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,23 +1948,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B15" t="n">
         <v>79014</v>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R15" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,12 +2045,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B16" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R16" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,17 +2151,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R17" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B75" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R75" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R76" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R79" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R80" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918830</v>
+        <v>126912889</v>
       </c>
       <c r="B3" t="n">
         <v>79014</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672770</v>
+        <v>672798</v>
       </c>
       <c r="R3" t="n">
-        <v>7090981</v>
+        <v>7091015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,26 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918815</v>
+        <v>126918830</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -884,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672767</v>
+        <v>672770</v>
       </c>
       <c r="R4" t="n">
-        <v>7090991</v>
+        <v>7090981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126912889</v>
+        <v>126918815</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +981,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672798</v>
+        <v>672767</v>
       </c>
       <c r="R5" t="n">
-        <v>7091015</v>
+        <v>7090991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,15 +1055,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1467,7 +1467,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919053</v>
+        <v>126912875</v>
       </c>
       <c r="B10" t="n">
         <v>79014</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672698</v>
+        <v>672751</v>
       </c>
       <c r="R10" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,23 +1552,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1603,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R11" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1766,10 +1762,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912726</v>
+        <v>126919053</v>
       </c>
       <c r="B13" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1773,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672750</v>
+        <v>672698</v>
       </c>
       <c r="R13" t="n">
-        <v>7091112</v>
+        <v>7091075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,19 +1847,23 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126912875</v>
+        <v>126919056</v>
       </c>
       <c r="B14" t="n">
         <v>79014</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672751</v>
+        <v>672702</v>
       </c>
       <c r="R14" t="n">
-        <v>7091113</v>
+        <v>7091127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,22 +1948,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126918821</v>
+        <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672752</v>
+        <v>672750</v>
       </c>
       <c r="R15" t="n">
-        <v>7091197</v>
+        <v>7091112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,23 +2049,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912882</v>
+        <v>126918827</v>
       </c>
       <c r="B16" t="n">
         <v>79014</v>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672738</v>
+        <v>672753</v>
       </c>
       <c r="R16" t="n">
-        <v>7091066</v>
+        <v>7091016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,22 +2146,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2173,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R17" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918827</v>
+        <v>126912935</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672753</v>
+        <v>672815</v>
       </c>
       <c r="R18" t="n">
-        <v>7091016</v>
+        <v>7090911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,19 +2344,15 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R22" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,17 +2749,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R23" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,14 +2846,14 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126919059</v>
+        <v>126913216</v>
       </c>
       <c r="B24" t="n">
         <v>79014</v>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672732</v>
+        <v>672804</v>
       </c>
       <c r="R24" t="n">
-        <v>7091173</v>
+        <v>7091051</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,12 +2938,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2954,7 +2954,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126913216</v>
+        <v>126919059</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672804</v>
+        <v>672732</v>
       </c>
       <c r="R25" t="n">
-        <v>7091051</v>
+        <v>7091173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,12 +3039,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912933</v>
+        <v>126912749</v>
       </c>
       <c r="B29" t="n">
-        <v>78681</v>
+        <v>92809</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672871</v>
+        <v>672946</v>
       </c>
       <c r="R29" t="n">
-        <v>7090905</v>
+        <v>7090821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3440,17 +3440,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912749</v>
+        <v>126912944</v>
       </c>
       <c r="B30" t="n">
-        <v>92809</v>
+        <v>78420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672946</v>
+        <v>672756</v>
       </c>
       <c r="R30" t="n">
-        <v>7090821</v>
+        <v>7091093</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,10 +3646,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912944</v>
+        <v>126912933</v>
       </c>
       <c r="B32" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,21 +3657,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3676,10 +3681,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672756</v>
+        <v>672871</v>
       </c>
       <c r="R32" t="n">
-        <v>7091093</v>
+        <v>7090905</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3714,11 +3719,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919057</v>
+        <v>126919054</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672730</v>
+        <v>672705</v>
       </c>
       <c r="R36" t="n">
-        <v>7091091</v>
+        <v>7091127</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912877</v>
+        <v>126919057</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672754</v>
+        <v>672730</v>
       </c>
       <c r="R37" t="n">
-        <v>7091099</v>
+        <v>7091091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,19 +4224,23 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R38" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4321,19 +4325,23 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919051</v>
+        <v>126912877</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4368,10 +4376,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672702</v>
+        <v>672754</v>
       </c>
       <c r="R39" t="n">
-        <v>7091061</v>
+        <v>7091099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4418,23 +4426,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919054</v>
+        <v>126918826</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4469,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672705</v>
+        <v>672744</v>
       </c>
       <c r="R40" t="n">
-        <v>7091127</v>
+        <v>7091079</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4519,12 +4523,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4535,7 +4539,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126918826</v>
+        <v>126912774</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4570,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672744</v>
+        <v>672889</v>
       </c>
       <c r="R41" t="n">
-        <v>7091079</v>
+        <v>7090793</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,19 +4624,15 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4733,32 +4733,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912887</v>
+        <v>126919016</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672750</v>
+        <v>672887</v>
       </c>
       <c r="R43" t="n">
-        <v>7091052</v>
+        <v>7090802</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,19 +4818,23 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912865</v>
+        <v>126918820</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -4865,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672783</v>
+        <v>672755</v>
       </c>
       <c r="R44" t="n">
-        <v>7091147</v>
+        <v>7091121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4915,19 +4919,23 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126918820</v>
+        <v>126912887</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -4962,10 +4970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672755</v>
+        <v>672750</v>
       </c>
       <c r="R45" t="n">
-        <v>7091121</v>
+        <v>7091052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5012,19 +5020,15 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5129,32 +5133,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919016</v>
+        <v>126912865</v>
       </c>
       <c r="B47" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5164,10 +5168,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672887</v>
+        <v>672783</v>
       </c>
       <c r="R47" t="n">
-        <v>7090802</v>
+        <v>7091147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,19 +5218,15 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919049</v>
+        <v>126919079</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>92616</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672651</v>
+        <v>672953</v>
       </c>
       <c r="R49" t="n">
-        <v>7091012</v>
+        <v>7090819</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,10 +5432,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B50" t="n">
-        <v>91344</v>
+        <v>79632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5443,21 +5443,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R50" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5529,32 +5529,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B51" t="n">
-        <v>92616</v>
+        <v>91344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R51" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5614,26 +5614,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912713</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5637,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672780</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7091043</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,15 +5711,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6022,32 +6022,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919060</v>
+        <v>126919018</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>56849</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6057,10 +6057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672791</v>
+        <v>672883</v>
       </c>
       <c r="R56" t="n">
-        <v>7091150</v>
+        <v>7090877</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6093,6 +6093,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6123,32 +6128,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919018</v>
+        <v>126912868</v>
       </c>
       <c r="B57" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6163,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672883</v>
+        <v>672779</v>
       </c>
       <c r="R57" t="n">
-        <v>7090877</v>
+        <v>7091147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6196,11 +6201,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6213,23 +6213,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912868</v>
+        <v>126912879</v>
       </c>
       <c r="B58" t="n">
         <v>79014</v>
@@ -6264,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672779</v>
+        <v>672751</v>
       </c>
       <c r="R58" t="n">
-        <v>7091147</v>
+        <v>7091095</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6326,7 +6322,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126912879</v>
+        <v>126919060</v>
       </c>
       <c r="B59" t="n">
         <v>79014</v>
@@ -6361,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672751</v>
+        <v>672791</v>
       </c>
       <c r="R59" t="n">
-        <v>7091095</v>
+        <v>7091150</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6411,15 +6407,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126913217</v>
+        <v>126912892</v>
       </c>
       <c r="B62" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672643</v>
+        <v>672787</v>
       </c>
       <c r="R62" t="n">
-        <v>7091013</v>
+        <v>7090995</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6702,26 +6702,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912892</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672787</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7090995</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,15 +6799,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Lars-Erik Nilsson, Liam Sebestyén, Martin Axegård, Alva Danielsson, Philipp Weiss, Cajsa Björkén, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B84" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R84" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R85" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B71" t="n">
-        <v>79014</v>
+        <v>57817</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,26 +7571,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7598,10 +7603,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R71" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7642,7 +7647,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7665,10 +7669,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B72" t="n">
-        <v>57817</v>
+        <v>79014</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7676,31 +7680,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7708,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R72" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7752,6 +7751,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>79014</v>
+        <v>91587</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R75" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>91587</v>
+        <v>79014</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R76" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -4038,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919054</v>
+        <v>126912877</v>
       </c>
       <c r="B36" t="n">
         <v>79014</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672705</v>
+        <v>672754</v>
       </c>
       <c r="R36" t="n">
-        <v>7091127</v>
+        <v>7091099</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,23 +4123,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919057</v>
+        <v>126918826</v>
       </c>
       <c r="B37" t="n">
         <v>79014</v>
@@ -4174,10 +4170,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672730</v>
+        <v>672744</v>
       </c>
       <c r="R37" t="n">
-        <v>7091091</v>
+        <v>7091079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,12 +4220,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4240,7 +4236,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919051</v>
+        <v>126912774</v>
       </c>
       <c r="B38" t="n">
         <v>79014</v>
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672702</v>
+        <v>672889</v>
       </c>
       <c r="R38" t="n">
-        <v>7091061</v>
+        <v>7090793</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,23 +4321,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912877</v>
+        <v>126919054</v>
       </c>
       <c r="B39" t="n">
         <v>79014</v>
@@ -4376,10 +4368,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672754</v>
+        <v>672705</v>
       </c>
       <c r="R39" t="n">
-        <v>7091099</v>
+        <v>7091127</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4426,19 +4418,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918826</v>
+        <v>126919057</v>
       </c>
       <c r="B40" t="n">
         <v>79014</v>
@@ -4473,10 +4469,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672744</v>
+        <v>672730</v>
       </c>
       <c r="R40" t="n">
-        <v>7091079</v>
+        <v>7091091</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,12 +4519,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4539,7 +4535,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B41" t="n">
         <v>79014</v>
@@ -4574,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R41" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4624,15 +4620,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4733,32 +4733,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126919016</v>
+        <v>126918820</v>
       </c>
       <c r="B43" t="n">
-        <v>57479</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672887</v>
+        <v>672755</v>
       </c>
       <c r="R43" t="n">
-        <v>7090802</v>
+        <v>7091121</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,12 +4818,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4834,7 +4834,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126918820</v>
+        <v>126912887</v>
       </c>
       <c r="B44" t="n">
         <v>79014</v>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672755</v>
+        <v>672750</v>
       </c>
       <c r="R44" t="n">
-        <v>7091121</v>
+        <v>7091052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,23 +4919,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912887</v>
+        <v>126913218</v>
       </c>
       <c r="B45" t="n">
         <v>79014</v>
@@ -4970,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672750</v>
+        <v>672656</v>
       </c>
       <c r="R45" t="n">
-        <v>7091052</v>
+        <v>7091011</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5020,19 +5016,23 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126913218</v>
+        <v>126912865</v>
       </c>
       <c r="B46" t="n">
         <v>79014</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672656</v>
+        <v>672783</v>
       </c>
       <c r="R46" t="n">
-        <v>7091011</v>
+        <v>7091147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,48 +5117,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912865</v>
+        <v>126919016</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>57479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5168,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672783</v>
+        <v>672887</v>
       </c>
       <c r="R47" t="n">
-        <v>7091147</v>
+        <v>7090802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,15 +5214,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126919049</v>
       </c>
       <c r="B49" t="n">
-        <v>92616</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672651</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091012</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5432,32 +5432,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B50" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R50" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,22 +5517,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B51" t="n">
-        <v>91344</v>
+        <v>79632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,21 +5544,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5626,10 +5630,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126912762</v>
       </c>
       <c r="B52" t="n">
-        <v>79014</v>
+        <v>91344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672743</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7091094</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5711,19 +5715,15 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5824,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126913223</v>
+        <v>126912723</v>
       </c>
       <c r="B54" t="n">
-        <v>79046</v>
+        <v>91248</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672862</v>
+        <v>672755</v>
       </c>
       <c r="R54" t="n">
-        <v>7090889</v>
+        <v>7091097</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,48 +5909,44 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912723</v>
+        <v>126919018</v>
       </c>
       <c r="B55" t="n">
-        <v>91248</v>
+        <v>56849</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3242</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5960,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672755</v>
+        <v>672883</v>
       </c>
       <c r="R55" t="n">
-        <v>7091097</v>
+        <v>7090877</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5998,6 +5994,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6010,44 +6011,48 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919018</v>
+        <v>126913223</v>
       </c>
       <c r="B56" t="n">
-        <v>56849</v>
+        <v>79046</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6057,10 +6062,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672883</v>
+        <v>672862</v>
       </c>
       <c r="R56" t="n">
-        <v>7090877</v>
+        <v>7090889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6095,11 +6100,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6112,12 +6112,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912934</v>
+        <v>126912884</v>
       </c>
       <c r="B60" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672873</v>
+        <v>672746</v>
       </c>
       <c r="R60" t="n">
-        <v>7090916</v>
+        <v>7091051</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6513,17 +6513,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912884</v>
+        <v>126912934</v>
       </c>
       <c r="B61" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672746</v>
+        <v>672873</v>
       </c>
       <c r="R61" t="n">
-        <v>7091051</v>
+        <v>7090916</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912928</v>
+        <v>126918815</v>
       </c>
       <c r="B2" t="n">
-        <v>92616</v>
+        <v>78776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672944</v>
+        <v>672767</v>
       </c>
       <c r="R2" t="n">
-        <v>7090839</v>
+        <v>7090991</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126912889</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +876,7 @@
         <v>126918830</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,32 +974,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>92620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R5" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,26 +1059,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>126912873</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>126919058</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>126913222</v>
       </c>
       <c r="B8" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912932</v>
+        <v>126912715</v>
       </c>
       <c r="B9" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672755</v>
+        <v>672914</v>
       </c>
       <c r="R9" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1470,7 +1470,7 @@
         <v>126912875</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>126918821</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912715</v>
+        <v>126919053</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672914</v>
+        <v>672698</v>
       </c>
       <c r="R12" t="n">
-        <v>7090807</v>
+        <v>7091075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,22 +1750,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919053</v>
+        <v>126919056</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1797,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672698</v>
+        <v>672702</v>
       </c>
       <c r="R13" t="n">
-        <v>7091075</v>
+        <v>7091127</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919056</v>
+        <v>126912932</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,21 +1878,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672702</v>
+        <v>672755</v>
       </c>
       <c r="R14" t="n">
-        <v>7091127</v>
+        <v>7091113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,26 +1952,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918827</v>
+        <v>126912935</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672753</v>
+        <v>672815</v>
       </c>
       <c r="R16" t="n">
-        <v>7091016</v>
+        <v>7090911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,26 +2146,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912882</v>
+        <v>126918827</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672738</v>
+        <v>672753</v>
       </c>
       <c r="R17" t="n">
-        <v>7091066</v>
+        <v>7091016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,22 +2243,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B18" t="n">
-        <v>78681</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R18" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2349,17 +2349,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126913219</v>
+        <v>126918828</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672627</v>
+        <v>672757</v>
       </c>
       <c r="R19" t="n">
-        <v>7091008</v>
+        <v>7091027</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,12 +2441,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2457,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918828</v>
+        <v>126918825</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672757</v>
+        <v>672764</v>
       </c>
       <c r="R20" t="n">
-        <v>7091027</v>
+        <v>7091153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918825</v>
+        <v>126913219</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672764</v>
+        <v>672627</v>
       </c>
       <c r="R21" t="n">
-        <v>7091153</v>
+        <v>7091008</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,12 +2643,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2662,7 +2662,7 @@
         <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
         <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2856,7 +2856,7 @@
         <v>126913216</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
         <v>126919059</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>126912870</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126912860</v>
+        <v>126918831</v>
       </c>
       <c r="B27" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672791</v>
+        <v>672756</v>
       </c>
       <c r="R27" t="n">
-        <v>7091154</v>
+        <v>7090952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,22 +3237,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918831</v>
+        <v>126912860</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3284,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672756</v>
+        <v>672791</v>
       </c>
       <c r="R28" t="n">
-        <v>7090952</v>
+        <v>7091154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3334,26 +3338,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>126912749</v>
       </c>
       <c r="B29" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912944</v>
+        <v>126912933</v>
       </c>
       <c r="B30" t="n">
-        <v>78420</v>
+        <v>78685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672756</v>
+        <v>672871</v>
       </c>
       <c r="R30" t="n">
-        <v>7091093</v>
+        <v>7090905</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,11 +3518,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3552,7 +3547,7 @@
         <v>126912717</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3646,10 +3641,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912933</v>
+        <v>126912944</v>
       </c>
       <c r="B32" t="n">
-        <v>78681</v>
+        <v>78424</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3657,21 +3652,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3681,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672871</v>
+        <v>672756</v>
       </c>
       <c r="R32" t="n">
-        <v>7090905</v>
+        <v>7091093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3719,6 +3714,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
         <v>126918824</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R34" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B35" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R35" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126912877</v>
+        <v>126919054</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672754</v>
+        <v>672705</v>
       </c>
       <c r="R36" t="n">
-        <v>7091099</v>
+        <v>7091127</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,22 +4123,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126918826</v>
+        <v>126919057</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4170,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672744</v>
+        <v>672730</v>
       </c>
       <c r="R37" t="n">
-        <v>7091079</v>
+        <v>7091091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4220,12 +4224,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
@@ -4236,10 +4240,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912774</v>
+        <v>126912877</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672889</v>
+        <v>672754</v>
       </c>
       <c r="R38" t="n">
-        <v>7090793</v>
+        <v>7091099</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4333,10 +4337,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919054</v>
+        <v>126919051</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4368,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672705</v>
+        <v>672702</v>
       </c>
       <c r="R39" t="n">
-        <v>7091127</v>
+        <v>7091061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4434,10 +4438,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919057</v>
+        <v>126918826</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4469,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672730</v>
+        <v>672744</v>
       </c>
       <c r="R40" t="n">
-        <v>7091091</v>
+        <v>7091079</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4519,12 +4523,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
@@ -4535,10 +4539,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919051</v>
+        <v>126912774</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4570,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672702</v>
+        <v>672889</v>
       </c>
       <c r="R41" t="n">
-        <v>7091061</v>
+        <v>7090793</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,48 +4624,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912927</v>
+        <v>126918820</v>
       </c>
       <c r="B42" t="n">
-        <v>92616</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672768</v>
+        <v>672755</v>
       </c>
       <c r="R42" t="n">
-        <v>7091045</v>
+        <v>7091121</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,44 +4721,48 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126918820</v>
+        <v>126912927</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>92620</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4768,10 +4772,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672755</v>
+        <v>672768</v>
       </c>
       <c r="R43" t="n">
-        <v>7091121</v>
+        <v>7091045</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,26 +4822,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>126912887</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>126913218</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5035,7 +5035,7 @@
         <v>126912865</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>126919016</v>
       </c>
       <c r="B47" t="n">
-        <v>57479</v>
+        <v>57483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         <v>126919050</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5342,21 +5342,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R49" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,48 +5416,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B50" t="n">
-        <v>92616</v>
+        <v>91348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R50" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,48 +5513,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B51" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5560,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R51" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,22 +5610,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912762</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>91344</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5637,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672743</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7091094</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,22 +5711,26 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>126912718</v>
       </c>
       <c r="B53" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912723</v>
+        <v>126912879</v>
       </c>
       <c r="B54" t="n">
-        <v>91248</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672755</v>
+        <v>672751</v>
       </c>
       <c r="R54" t="n">
-        <v>7091097</v>
+        <v>7091095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,32 +5921,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919018</v>
+        <v>126919060</v>
       </c>
       <c r="B55" t="n">
-        <v>56849</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672883</v>
+        <v>672791</v>
       </c>
       <c r="R55" t="n">
-        <v>7090877</v>
+        <v>7091150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5992,11 +5992,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6027,10 +6022,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126913223</v>
+        <v>126912868</v>
       </c>
       <c r="B56" t="n">
-        <v>79046</v>
+        <v>79018</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6038,21 +6033,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6062,10 +6057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672862</v>
+        <v>672779</v>
       </c>
       <c r="R56" t="n">
-        <v>7090889</v>
+        <v>7091147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,26 +6107,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912868</v>
+        <v>126912723</v>
       </c>
       <c r="B57" t="n">
-        <v>79014</v>
+        <v>91252</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6139,21 +6130,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6163,10 +6154,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672779</v>
+        <v>672755</v>
       </c>
       <c r="R57" t="n">
-        <v>7091147</v>
+        <v>7091097</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6225,10 +6216,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912879</v>
+        <v>126913223</v>
       </c>
       <c r="B58" t="n">
-        <v>79014</v>
+        <v>79050</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,21 +6227,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672751</v>
+        <v>672862</v>
       </c>
       <c r="R58" t="n">
-        <v>7091095</v>
+        <v>7090889</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,44 +6301,48 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919060</v>
+        <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>79014</v>
+        <v>56853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6352,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672791</v>
+        <v>672883</v>
       </c>
       <c r="R59" t="n">
-        <v>7091150</v>
+        <v>7090877</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6393,6 +6388,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912884</v>
+        <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672746</v>
+        <v>672873</v>
       </c>
       <c r="R60" t="n">
-        <v>7091051</v>
+        <v>7090916</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912934</v>
+        <v>126913217</v>
       </c>
       <c r="B61" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672873</v>
+        <v>672643</v>
       </c>
       <c r="R61" t="n">
-        <v>7090916</v>
+        <v>7091013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,22 +6605,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>126912892</v>
       </c>
       <c r="B62" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126913217</v>
+        <v>126912884</v>
       </c>
       <c r="B63" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672643</v>
+        <v>672746</v>
       </c>
       <c r="R63" t="n">
-        <v>7091013</v>
+        <v>7091051</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6799,26 +6803,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126917430</v>
       </c>
       <c r="B64" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>126917438</v>
       </c>
       <c r="B65" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126917439</v>
       </c>
       <c r="B66" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>126917436</v>
       </c>
       <c r="B69" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>126917440</v>
       </c>
       <c r="B70" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>57817</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,31 +7571,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7647,6 +7642,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7669,10 +7665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>79014</v>
+        <v>57821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7680,26 +7676,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7707,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R72" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7751,7 +7752,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7777,7 +7777,7 @@
         <v>126917444</v>
       </c>
       <c r="B73" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>126917442</v>
       </c>
       <c r="B74" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B75" t="n">
-        <v>91587</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R75" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B76" t="n">
-        <v>79014</v>
+        <v>91591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R76" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8197,7 +8197,7 @@
         <v>126917432</v>
       </c>
       <c r="B77" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>126913591</v>
       </c>
       <c r="B78" t="n">
-        <v>78681</v>
+        <v>78685</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>126913586</v>
       </c>
       <c r="B81" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>126913587</v>
       </c>
       <c r="B82" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>126913589</v>
       </c>
       <c r="B83" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>126913582</v>
       </c>
       <c r="B84" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>126913588</v>
       </c>
       <c r="B85" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>126913584</v>
       </c>
       <c r="B86" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>126913585</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>126913593</v>
       </c>
       <c r="B88" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>78776</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R2" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,15 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -974,32 +970,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126912928</v>
+        <v>126918815</v>
       </c>
       <c r="B5" t="n">
-        <v>92620</v>
+        <v>78776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672944</v>
+        <v>672767</v>
       </c>
       <c r="R5" t="n">
-        <v>7090839</v>
+        <v>7090991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,15 +1055,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912715</v>
+        <v>126912932</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672914</v>
+        <v>672755</v>
       </c>
       <c r="R9" t="n">
-        <v>7090807</v>
+        <v>7091113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126912715</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672914</v>
       </c>
       <c r="R10" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126919053</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672698</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7091075</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1665,7 +1665,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919053</v>
+        <v>126912875</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672698</v>
+        <v>672751</v>
       </c>
       <c r="R12" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,23 +1750,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1801,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R13" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1851,12 +1847,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -1867,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126912932</v>
+        <v>126919056</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1874,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672755</v>
+        <v>672702</v>
       </c>
       <c r="R14" t="n">
-        <v>7091113</v>
+        <v>7091127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,15 +1948,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912935</v>
+        <v>126918827</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672815</v>
+        <v>672753</v>
       </c>
       <c r="R16" t="n">
-        <v>7090911</v>
+        <v>7091016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,19 +2146,23 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918827</v>
+        <v>126912882</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672753</v>
+        <v>672738</v>
       </c>
       <c r="R17" t="n">
-        <v>7091016</v>
+        <v>7091066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,26 +2247,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R18" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2356,7 +2356,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126918828</v>
+        <v>126913219</v>
       </c>
       <c r="B19" t="n">
         <v>79018</v>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672757</v>
+        <v>672627</v>
       </c>
       <c r="R19" t="n">
-        <v>7091027</v>
+        <v>7091008</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,12 +2441,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2457,7 +2457,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918825</v>
+        <v>126918828</v>
       </c>
       <c r="B20" t="n">
         <v>79018</v>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672764</v>
+        <v>672757</v>
       </c>
       <c r="R20" t="n">
-        <v>7091153</v>
+        <v>7091027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126913219</v>
+        <v>126918825</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672627</v>
+        <v>672764</v>
       </c>
       <c r="R21" t="n">
-        <v>7091008</v>
+        <v>7091153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,12 +2643,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R22" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R23" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3152,7 +3152,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918831</v>
+        <v>126912860</v>
       </c>
       <c r="B27" t="n">
         <v>79018</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672756</v>
+        <v>672791</v>
       </c>
       <c r="R27" t="n">
-        <v>7090952</v>
+        <v>7091154</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,23 +3237,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912860</v>
+        <v>126918831</v>
       </c>
       <c r="B28" t="n">
         <v>79018</v>
@@ -3288,10 +3284,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672791</v>
+        <v>672756</v>
       </c>
       <c r="R28" t="n">
-        <v>7091154</v>
+        <v>7090952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3338,22 +3334,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912749</v>
+        <v>126912933</v>
       </c>
       <c r="B29" t="n">
-        <v>92813</v>
+        <v>78685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672946</v>
+        <v>672871</v>
       </c>
       <c r="R29" t="n">
-        <v>7090821</v>
+        <v>7090905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912933</v>
+        <v>126912749</v>
       </c>
       <c r="B30" t="n">
-        <v>78685</v>
+        <v>92813</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672871</v>
+        <v>672946</v>
       </c>
       <c r="R30" t="n">
-        <v>7090905</v>
+        <v>7090821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R34" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R35" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919054</v>
+        <v>126918826</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672705</v>
+        <v>672744</v>
       </c>
       <c r="R36" t="n">
-        <v>7091127</v>
+        <v>7091079</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,12 +4123,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4139,7 +4139,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919057</v>
+        <v>126919054</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672730</v>
+        <v>672705</v>
       </c>
       <c r="R37" t="n">
-        <v>7091091</v>
+        <v>7091127</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912877</v>
+        <v>126919057</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672754</v>
+        <v>672730</v>
       </c>
       <c r="R38" t="n">
-        <v>7091099</v>
+        <v>7091091</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,19 +4325,23 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919051</v>
+        <v>126912877</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4372,10 +4376,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672702</v>
+        <v>672754</v>
       </c>
       <c r="R39" t="n">
-        <v>7091061</v>
+        <v>7091099</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,23 +4426,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126918826</v>
+        <v>126912774</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672744</v>
+        <v>672889</v>
       </c>
       <c r="R40" t="n">
-        <v>7091079</v>
+        <v>7090793</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,23 +4523,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B41" t="n">
         <v>79018</v>
@@ -4574,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R41" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4624,44 +4620,48 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126918820</v>
+        <v>126912927</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672755</v>
+        <v>672768</v>
       </c>
       <c r="R42" t="n">
-        <v>7091121</v>
+        <v>7091045</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4721,48 +4721,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912927</v>
+        <v>126918820</v>
       </c>
       <c r="B43" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4772,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672768</v>
+        <v>672755</v>
       </c>
       <c r="R43" t="n">
-        <v>7091045</v>
+        <v>7091121</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4822,19 +4818,23 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912887</v>
+        <v>126913218</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672750</v>
+        <v>672656</v>
       </c>
       <c r="R44" t="n">
-        <v>7091052</v>
+        <v>7091011</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,19 +4919,23 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913218</v>
+        <v>126912865</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -4966,10 +4970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672656</v>
+        <v>672783</v>
       </c>
       <c r="R45" t="n">
-        <v>7091011</v>
+        <v>7091147</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5016,23 +5020,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912865</v>
+        <v>126912887</v>
       </c>
       <c r="B46" t="n">
         <v>79018</v>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672783</v>
+        <v>672750</v>
       </c>
       <c r="R46" t="n">
-        <v>7091147</v>
+        <v>7091052</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R49" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,22 +5416,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912762</v>
+        <v>126919049</v>
       </c>
       <c r="B50" t="n">
-        <v>91348</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5439,21 +5443,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672743</v>
+        <v>672651</v>
       </c>
       <c r="R50" t="n">
-        <v>7091094</v>
+        <v>7091012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5513,44 +5517,48 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B51" t="n">
-        <v>92620</v>
+        <v>91348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5560,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R51" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5610,26 +5618,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5711,19 +5715,15 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5824,7 +5824,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912879</v>
+        <v>126912868</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672751</v>
+        <v>672779</v>
       </c>
       <c r="R54" t="n">
-        <v>7091095</v>
+        <v>7091147</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126919060</v>
+        <v>126912879</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672791</v>
+        <v>672751</v>
       </c>
       <c r="R55" t="n">
-        <v>7091150</v>
+        <v>7091095</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,48 +6006,44 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912868</v>
+        <v>126919018</v>
       </c>
       <c r="B56" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6057,10 +6053,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672779</v>
+        <v>672883</v>
       </c>
       <c r="R56" t="n">
-        <v>7091147</v>
+        <v>7090877</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6095,6 +6091,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6107,22 +6108,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912723</v>
+        <v>126913223</v>
       </c>
       <c r="B57" t="n">
-        <v>91252</v>
+        <v>79050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,21 +6135,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6154,10 +6159,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672755</v>
+        <v>672862</v>
       </c>
       <c r="R57" t="n">
-        <v>7091097</v>
+        <v>7090889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6204,22 +6209,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126913223</v>
+        <v>126912723</v>
       </c>
       <c r="B58" t="n">
-        <v>79050</v>
+        <v>91252</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6227,21 +6236,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>185</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6251,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672862</v>
+        <v>672755</v>
       </c>
       <c r="R58" t="n">
-        <v>7090889</v>
+        <v>7091097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6301,48 +6310,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919018</v>
+        <v>126919060</v>
       </c>
       <c r="B59" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6352,10 +6357,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>672791</v>
       </c>
       <c r="R59" t="n">
-        <v>7090877</v>
+        <v>7091150</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6388,11 +6393,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126912884</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672746</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7091051</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,19 +6605,15 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6718,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912884</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672746</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7091051</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,15 +6799,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7135,37 +7135,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7173,10 +7174,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R67" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7211,13 +7212,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7240,38 +7245,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B68" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7279,10 +7283,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R68" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7317,17 +7321,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,26 +7571,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7598,10 +7603,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R71" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7642,7 +7647,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7665,10 +7669,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B72" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7676,31 +7680,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7708,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R72" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7752,6 +7751,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R75" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R76" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R84" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R85" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912715</v>
+        <v>126912875</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672914</v>
+        <v>672751</v>
       </c>
       <c r="R10" t="n">
-        <v>7090807</v>
+        <v>7091113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919053</v>
+        <v>126918821</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672698</v>
+        <v>672752</v>
       </c>
       <c r="R11" t="n">
-        <v>7091075</v>
+        <v>7091197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912875</v>
+        <v>126912715</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672751</v>
+        <v>672914</v>
       </c>
       <c r="R12" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1762,7 +1762,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126918821</v>
+        <v>126919053</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1797,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672752</v>
+        <v>672698</v>
       </c>
       <c r="R13" t="n">
-        <v>7091197</v>
+        <v>7091075</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,12 +1847,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B49" t="n">
-        <v>92620</v>
+        <v>91348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,26 +5416,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5443,21 +5439,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R50" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,48 +5513,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126919079</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5560,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672953</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7090819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,22 +5610,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912713</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5637,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672780</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7091043</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,15 +5711,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5824,7 +5824,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912868</v>
+        <v>126919060</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672779</v>
+        <v>672791</v>
       </c>
       <c r="R54" t="n">
-        <v>7091147</v>
+        <v>7091150</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,22 +5909,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912879</v>
+        <v>126913223</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,21 +5936,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672751</v>
+        <v>672862</v>
       </c>
       <c r="R55" t="n">
-        <v>7091095</v>
+        <v>7090889</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,44 +6010,48 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919018</v>
+        <v>126912723</v>
       </c>
       <c r="B56" t="n">
-        <v>56853</v>
+        <v>91252</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>3242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6053,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672883</v>
+        <v>672755</v>
       </c>
       <c r="R56" t="n">
-        <v>7090877</v>
+        <v>7091097</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6091,11 +6099,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6108,26 +6111,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126913223</v>
+        <v>126912868</v>
       </c>
       <c r="B57" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6135,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6159,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672862</v>
+        <v>672779</v>
       </c>
       <c r="R57" t="n">
-        <v>7090889</v>
+        <v>7091147</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,26 +6208,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912723</v>
+        <v>126912879</v>
       </c>
       <c r="B58" t="n">
-        <v>91252</v>
+        <v>79018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6236,21 +6231,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672755</v>
+        <v>672751</v>
       </c>
       <c r="R58" t="n">
-        <v>7091097</v>
+        <v>7091095</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6322,32 +6317,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919060</v>
+        <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6357,10 +6352,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672791</v>
+        <v>672883</v>
       </c>
       <c r="R59" t="n">
-        <v>7091150</v>
+        <v>7090877</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6393,6 +6388,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7135,38 +7135,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7174,10 +7173,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R67" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7212,17 +7211,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7245,37 +7240,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7283,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R68" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7321,13 +7317,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912928</v>
+        <v>126912889</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672944</v>
+        <v>672798</v>
       </c>
       <c r="R2" t="n">
-        <v>7090839</v>
+        <v>7091015</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912889</v>
+        <v>126918830</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672798</v>
+        <v>672770</v>
       </c>
       <c r="R3" t="n">
-        <v>7091015</v>
+        <v>7090981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,44 +857,48 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918830</v>
+        <v>126912928</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672770</v>
+        <v>672944</v>
       </c>
       <c r="R4" t="n">
-        <v>7090981</v>
+        <v>7090839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +958,15 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126918827</v>
+        <v>126912935</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672753</v>
+        <v>672815</v>
       </c>
       <c r="R16" t="n">
-        <v>7091016</v>
+        <v>7090911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,23 +2146,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912882</v>
+        <v>126918827</v>
       </c>
       <c r="B17" t="n">
         <v>79018</v>
@@ -2197,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672738</v>
+        <v>672753</v>
       </c>
       <c r="R17" t="n">
-        <v>7091066</v>
+        <v>7091016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,22 +2243,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B18" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R18" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912762</v>
+        <v>126919079</v>
       </c>
       <c r="B49" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672743</v>
+        <v>672953</v>
       </c>
       <c r="R49" t="n">
-        <v>7091094</v>
+        <v>7090819</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,22 +5416,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912713</v>
+        <v>126919049</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5439,21 +5443,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672780</v>
+        <v>672651</v>
       </c>
       <c r="R50" t="n">
-        <v>7091043</v>
+        <v>7091012</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5513,44 +5517,48 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B51" t="n">
-        <v>92620</v>
+        <v>91348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5560,10 +5568,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R51" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5610,26 +5618,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126912713</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5637,21 +5641,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5661,10 +5665,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672780</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7091043</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5711,19 +5715,15 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,31 +7571,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7647,6 +7642,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7669,10 +7665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7680,26 +7676,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7707,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R72" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7751,7 +7752,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B84" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R84" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R85" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912889</v>
+        <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>92620</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672798</v>
+        <v>672944</v>
       </c>
       <c r="R2" t="n">
-        <v>7091015</v>
+        <v>7090839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918830</v>
+        <v>126912889</v>
       </c>
       <c r="B3" t="n">
         <v>79018</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672770</v>
+        <v>672798</v>
       </c>
       <c r="R3" t="n">
-        <v>7090981</v>
+        <v>7091015</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,48 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126912928</v>
+        <v>126918830</v>
       </c>
       <c r="B4" t="n">
-        <v>92620</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -908,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672944</v>
+        <v>672770</v>
       </c>
       <c r="R4" t="n">
-        <v>7090839</v>
+        <v>7090981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -958,15 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,32 +1071,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126912873</v>
+        <v>126913222</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672756</v>
+        <v>672883</v>
       </c>
       <c r="R6" t="n">
-        <v>7091126</v>
+        <v>7090921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,15 +1156,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,32 +1273,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126913222</v>
+        <v>126912873</v>
       </c>
       <c r="B8" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672883</v>
+        <v>672756</v>
       </c>
       <c r="R8" t="n">
-        <v>7090921</v>
+        <v>7091126</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,19 +1358,15 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126912715</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672914</v>
       </c>
       <c r="R10" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126919053</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672698</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7091075</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912715</v>
+        <v>126919056</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672914</v>
+        <v>672702</v>
       </c>
       <c r="R12" t="n">
-        <v>7090807</v>
+        <v>7091127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,19 +1750,23 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126919053</v>
+        <v>126912875</v>
       </c>
       <c r="B13" t="n">
         <v>79018</v>
@@ -1797,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672698</v>
+        <v>672751</v>
       </c>
       <c r="R13" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1847,23 +1851,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B14" t="n">
         <v>79018</v>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R14" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B16" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R16" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,10 +2158,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126918827</v>
+        <v>126912935</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672753</v>
+        <v>672815</v>
       </c>
       <c r="R17" t="n">
-        <v>7091016</v>
+        <v>7090911</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,23 +2243,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126912882</v>
+        <v>126918827</v>
       </c>
       <c r="B18" t="n">
         <v>79018</v>
@@ -2294,10 +2290,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672738</v>
+        <v>672753</v>
       </c>
       <c r="R18" t="n">
-        <v>7091066</v>
+        <v>7091016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2344,15 +2340,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R22" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R23" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912933</v>
+        <v>126912749</v>
       </c>
       <c r="B29" t="n">
-        <v>78685</v>
+        <v>92813</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672871</v>
+        <v>672946</v>
       </c>
       <c r="R29" t="n">
-        <v>7090905</v>
+        <v>7090821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912749</v>
+        <v>126912933</v>
       </c>
       <c r="B30" t="n">
-        <v>92813</v>
+        <v>78685</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672946</v>
+        <v>672871</v>
       </c>
       <c r="R30" t="n">
-        <v>7090821</v>
+        <v>7090905</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R34" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B35" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R35" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126918826</v>
+        <v>126919057</v>
       </c>
       <c r="B36" t="n">
         <v>79018</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672744</v>
+        <v>672730</v>
       </c>
       <c r="R36" t="n">
-        <v>7091079</v>
+        <v>7091091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,12 +4123,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
@@ -4139,7 +4139,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126919054</v>
+        <v>126912877</v>
       </c>
       <c r="B37" t="n">
         <v>79018</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672705</v>
+        <v>672754</v>
       </c>
       <c r="R37" t="n">
-        <v>7091127</v>
+        <v>7091099</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,23 +4224,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919057</v>
+        <v>126918826</v>
       </c>
       <c r="B38" t="n">
         <v>79018</v>
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672730</v>
+        <v>672744</v>
       </c>
       <c r="R38" t="n">
-        <v>7091091</v>
+        <v>7091079</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,12 +4321,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
@@ -4341,7 +4337,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912877</v>
+        <v>126919051</v>
       </c>
       <c r="B39" t="n">
         <v>79018</v>
@@ -4376,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672754</v>
+        <v>672702</v>
       </c>
       <c r="R39" t="n">
-        <v>7091099</v>
+        <v>7091061</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4426,19 +4422,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126912774</v>
+        <v>126919054</v>
       </c>
       <c r="B40" t="n">
         <v>79018</v>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672889</v>
+        <v>672705</v>
       </c>
       <c r="R40" t="n">
-        <v>7090793</v>
+        <v>7091127</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4523,19 +4523,23 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919051</v>
+        <v>126912774</v>
       </c>
       <c r="B41" t="n">
         <v>79018</v>
@@ -4570,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672702</v>
+        <v>672889</v>
       </c>
       <c r="R41" t="n">
-        <v>7091061</v>
+        <v>7090793</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,19 +4624,15 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4733,7 +4733,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126918820</v>
+        <v>126913218</v>
       </c>
       <c r="B43" t="n">
         <v>79018</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672755</v>
+        <v>672656</v>
       </c>
       <c r="R43" t="n">
-        <v>7091121</v>
+        <v>7091011</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,12 +4818,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -4834,7 +4834,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126913218</v>
+        <v>126918820</v>
       </c>
       <c r="B44" t="n">
         <v>79018</v>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672656</v>
+        <v>672755</v>
       </c>
       <c r="R44" t="n">
-        <v>7091011</v>
+        <v>7091121</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,12 +4919,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -4935,7 +4935,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912865</v>
+        <v>126912887</v>
       </c>
       <c r="B45" t="n">
         <v>79018</v>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672783</v>
+        <v>672750</v>
       </c>
       <c r="R45" t="n">
-        <v>7091147</v>
+        <v>7091052</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5032,32 +5032,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912887</v>
+        <v>126919016</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>57483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672750</v>
+        <v>672887</v>
       </c>
       <c r="R46" t="n">
-        <v>7091052</v>
+        <v>7090802</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,44 +5117,48 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919016</v>
+        <v>126912865</v>
       </c>
       <c r="B47" t="n">
-        <v>57483</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5164,10 +5168,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672887</v>
+        <v>672783</v>
       </c>
       <c r="R47" t="n">
-        <v>7090802</v>
+        <v>7091147</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,19 +5218,15 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126912713</v>
       </c>
       <c r="B49" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672780</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091043</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,26 +5416,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126919049</v>
+        <v>126912762</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>91348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5443,21 +5439,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672651</v>
+        <v>672743</v>
       </c>
       <c r="R50" t="n">
-        <v>7091012</v>
+        <v>7091094</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,48 +5513,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126919079</v>
       </c>
       <c r="B51" t="n">
-        <v>91348</v>
+        <v>92620</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5568,10 +5560,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672953</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7090819</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5618,22 +5610,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126912713</v>
+        <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5641,21 +5637,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5665,10 +5661,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672780</v>
+        <v>672651</v>
       </c>
       <c r="R52" t="n">
-        <v>7091043</v>
+        <v>7091012</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5715,15 +5711,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5824,32 +5824,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126919060</v>
+        <v>126919018</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672791</v>
+        <v>672883</v>
       </c>
       <c r="R54" t="n">
-        <v>7091150</v>
+        <v>7090877</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5895,6 +5895,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5925,10 +5930,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913223</v>
+        <v>126912879</v>
       </c>
       <c r="B55" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5936,21 +5941,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5960,10 +5965,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672862</v>
+        <v>672751</v>
       </c>
       <c r="R55" t="n">
-        <v>7090889</v>
+        <v>7091095</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6010,19 +6015,15 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6123,10 +6124,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912868</v>
+        <v>126913223</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6134,21 +6135,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6158,10 +6159,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672779</v>
+        <v>672862</v>
       </c>
       <c r="R57" t="n">
-        <v>7091147</v>
+        <v>7090889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6208,19 +6209,23 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912879</v>
+        <v>126919060</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6255,10 +6260,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672751</v>
+        <v>672791</v>
       </c>
       <c r="R58" t="n">
-        <v>7091095</v>
+        <v>7091150</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6305,44 +6310,48 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919018</v>
+        <v>126912868</v>
       </c>
       <c r="B59" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6352,10 +6361,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>672779</v>
       </c>
       <c r="R59" t="n">
-        <v>7090877</v>
+        <v>7091147</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6390,11 +6399,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6407,26 +6411,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912934</v>
+        <v>126912892</v>
       </c>
       <c r="B60" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672873</v>
+        <v>672787</v>
       </c>
       <c r="R60" t="n">
-        <v>7090916</v>
+        <v>7090995</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6617,10 +6617,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912892</v>
+        <v>126912934</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6628,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6652,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672787</v>
+        <v>672873</v>
       </c>
       <c r="R62" t="n">
-        <v>7090995</v>
+        <v>7090916</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7135,37 +7135,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7173,10 +7174,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R67" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7211,13 +7212,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7240,38 +7245,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B68" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7279,10 +7283,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R68" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7317,17 +7321,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B79" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R79" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B80" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R80" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -1172,7 +1172,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126919058</v>
+        <v>126912873</v>
       </c>
       <c r="B7" t="n">
         <v>79018</v>
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672737</v>
+        <v>672756</v>
       </c>
       <c r="R7" t="n">
-        <v>7091090</v>
+        <v>7091126</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,23 +1257,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126912873</v>
+        <v>126919058</v>
       </c>
       <c r="B8" t="n">
         <v>79018</v>
@@ -1308,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672756</v>
+        <v>672737</v>
       </c>
       <c r="R8" t="n">
-        <v>7091126</v>
+        <v>7091090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,22 +1354,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912932</v>
+        <v>126919053</v>
       </c>
       <c r="B9" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672755</v>
+        <v>672698</v>
       </c>
       <c r="R9" t="n">
-        <v>7091113</v>
+        <v>7091075</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,22 +1455,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912715</v>
+        <v>126919056</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672914</v>
+        <v>672702</v>
       </c>
       <c r="R10" t="n">
-        <v>7090807</v>
+        <v>7091127</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,19 +1556,23 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126919053</v>
+        <v>126912875</v>
       </c>
       <c r="B11" t="n">
         <v>79018</v>
@@ -1599,10 +1607,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672698</v>
+        <v>672751</v>
       </c>
       <c r="R11" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,23 +1657,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B12" t="n">
         <v>79018</v>
@@ -1700,10 +1704,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R12" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,12 +1754,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1766,10 +1770,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912875</v>
+        <v>126912726</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1781,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672751</v>
+        <v>672750</v>
       </c>
       <c r="R13" t="n">
-        <v>7091113</v>
+        <v>7091112</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918821</v>
+        <v>126912932</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,21 +1878,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1898,10 +1902,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672752</v>
+        <v>672755</v>
       </c>
       <c r="R14" t="n">
-        <v>7091197</v>
+        <v>7091113</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,26 +1952,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912726</v>
+        <v>126912715</v>
       </c>
       <c r="B15" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672750</v>
+        <v>672914</v>
       </c>
       <c r="R15" t="n">
-        <v>7091112</v>
+        <v>7090807</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -5824,32 +5824,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126919018</v>
+        <v>126912879</v>
       </c>
       <c r="B54" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672883</v>
+        <v>672751</v>
       </c>
       <c r="R54" t="n">
-        <v>7090877</v>
+        <v>7091095</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5897,11 +5897,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5914,26 +5909,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912879</v>
+        <v>126912723</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>91252</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5941,21 +5932,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5965,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672751</v>
+        <v>672755</v>
       </c>
       <c r="R55" t="n">
-        <v>7091095</v>
+        <v>7091097</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6027,10 +6018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912723</v>
+        <v>126913223</v>
       </c>
       <c r="B56" t="n">
-        <v>91252</v>
+        <v>79050</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6038,21 +6029,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6062,10 +6053,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672755</v>
+        <v>672862</v>
       </c>
       <c r="R56" t="n">
-        <v>7091097</v>
+        <v>7090889</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6112,22 +6103,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126913223</v>
+        <v>126919060</v>
       </c>
       <c r="B57" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6135,21 +6130,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6159,10 +6154,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672862</v>
+        <v>672791</v>
       </c>
       <c r="R57" t="n">
-        <v>7090889</v>
+        <v>7091150</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6209,12 +6204,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6225,7 +6220,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919060</v>
+        <v>126912868</v>
       </c>
       <c r="B58" t="n">
         <v>79018</v>
@@ -6260,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672791</v>
+        <v>672779</v>
       </c>
       <c r="R58" t="n">
-        <v>7091150</v>
+        <v>7091147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,48 +6305,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126912868</v>
+        <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6361,10 +6352,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672779</v>
+        <v>672883</v>
       </c>
       <c r="R59" t="n">
-        <v>7091147</v>
+        <v>7090877</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6399,6 +6390,11 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6411,22 +6407,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY59" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912892</v>
+        <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672787</v>
+        <v>672873</v>
       </c>
       <c r="R60" t="n">
-        <v>7090995</v>
+        <v>7090916</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912884</v>
+        <v>126913217</v>
       </c>
       <c r="B61" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672746</v>
+        <v>672643</v>
       </c>
       <c r="R61" t="n">
-        <v>7091051</v>
+        <v>7091013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,22 +6605,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912934</v>
+        <v>126912892</v>
       </c>
       <c r="B62" t="n">
-        <v>78685</v>
+        <v>79018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6628,21 +6632,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6652,10 +6656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672873</v>
+        <v>672787</v>
       </c>
       <c r="R62" t="n">
-        <v>7090916</v>
+        <v>7090995</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6714,10 +6718,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126913217</v>
+        <v>126912884</v>
       </c>
       <c r="B63" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672643</v>
+        <v>672746</v>
       </c>
       <c r="R63" t="n">
-        <v>7091013</v>
+        <v>7091051</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6799,19 +6803,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7135,38 +7135,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>56853</v>
+        <v>79018</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7174,10 +7173,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R67" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7212,17 +7211,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7245,37 +7240,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>79018</v>
+        <v>56853</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7283,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R68" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7321,13 +7317,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B71" t="n">
-        <v>79018</v>
+        <v>57821</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,26 +7571,31 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7598,10 +7603,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R71" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7642,7 +7647,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7665,10 +7669,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B72" t="n">
-        <v>57821</v>
+        <v>79018</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7676,31 +7680,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7708,10 +7707,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R72" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7752,6 +7751,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B75" t="n">
-        <v>91591</v>
+        <v>79018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R75" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B76" t="n">
-        <v>79018</v>
+        <v>91591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R76" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R84" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79050</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R85" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126912889</v>
+        <v>126918830</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672798</v>
+        <v>672770</v>
       </c>
       <c r="R3" t="n">
-        <v>7091015</v>
+        <v>7090981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126918830</v>
+        <v>126912889</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672770</v>
+        <v>672798</v>
       </c>
       <c r="R4" t="n">
-        <v>7090981</v>
+        <v>7091015</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,26 +958,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>126918815</v>
       </c>
       <c r="B5" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>126913222</v>
       </c>
       <c r="B6" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>126912873</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>126919058</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126919053</v>
+        <v>126912932</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672698</v>
+        <v>672755</v>
       </c>
       <c r="R9" t="n">
-        <v>7091075</v>
+        <v>7091113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,26 +1455,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>126919056</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1572,10 +1568,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126912875</v>
+        <v>126912715</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,21 +1579,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1607,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672751</v>
+        <v>672914</v>
       </c>
       <c r="R11" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126918821</v>
+        <v>126912875</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1704,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672752</v>
+        <v>672751</v>
       </c>
       <c r="R12" t="n">
-        <v>7091197</v>
+        <v>7091113</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,26 +1750,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>126912726</v>
       </c>
       <c r="B13" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1867,10 +1859,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126912932</v>
+        <v>126918821</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1870,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672755</v>
+        <v>672752</v>
       </c>
       <c r="R14" t="n">
-        <v>7091113</v>
+        <v>7091197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,22 +1944,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912715</v>
+        <v>126919053</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1971,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +1995,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672914</v>
+        <v>672698</v>
       </c>
       <c r="R15" t="n">
-        <v>7090807</v>
+        <v>7091075</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,22 +2045,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912882</v>
+        <v>126912935</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672738</v>
+        <v>672815</v>
       </c>
       <c r="R16" t="n">
-        <v>7091066</v>
+        <v>7090911</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,17 +2151,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912935</v>
+        <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2169,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672815</v>
+        <v>672738</v>
       </c>
       <c r="R17" t="n">
-        <v>7090911</v>
+        <v>7091066</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
         <v>126918827</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>126913219</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918828</v>
+        <v>126918825</v>
       </c>
       <c r="B20" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672757</v>
+        <v>672764</v>
       </c>
       <c r="R20" t="n">
-        <v>7091027</v>
+        <v>7091153</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918825</v>
+        <v>126918828</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672764</v>
+        <v>672757</v>
       </c>
       <c r="R21" t="n">
-        <v>7091153</v>
+        <v>7091027</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R22" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R23" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126913216</v>
+        <v>126919059</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672804</v>
+        <v>672732</v>
       </c>
       <c r="R24" t="n">
-        <v>7091051</v>
+        <v>7091173</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,12 +2938,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126919059</v>
+        <v>126913216</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672732</v>
+        <v>672804</v>
       </c>
       <c r="R25" t="n">
-        <v>7091173</v>
+        <v>7091051</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,12 +3039,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v>126912870</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         <v>126912860</v>
       </c>
       <c r="B27" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         <v>126918831</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3350,10 +3350,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912749</v>
+        <v>126912717</v>
       </c>
       <c r="B29" t="n">
-        <v>92813</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672946</v>
+        <v>672735</v>
       </c>
       <c r="R29" t="n">
-        <v>7090821</v>
+        <v>7091083</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912933</v>
+        <v>126912944</v>
       </c>
       <c r="B30" t="n">
-        <v>78685</v>
+        <v>78426</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672871</v>
+        <v>672756</v>
       </c>
       <c r="R30" t="n">
-        <v>7090905</v>
+        <v>7091093</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,6 +3518,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3544,10 +3549,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912717</v>
+        <v>126912933</v>
       </c>
       <c r="B31" t="n">
-        <v>79636</v>
+        <v>78687</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3555,21 +3560,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3579,10 +3584,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672735</v>
+        <v>672871</v>
       </c>
       <c r="R31" t="n">
-        <v>7091083</v>
+        <v>7090905</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3641,10 +3646,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912944</v>
+        <v>126912749</v>
       </c>
       <c r="B32" t="n">
-        <v>78424</v>
+        <v>92815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,21 +3657,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3676,10 +3681,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672756</v>
+        <v>672946</v>
       </c>
       <c r="R32" t="n">
-        <v>7091093</v>
+        <v>7090821</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3712,11 +3717,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3746,7 +3746,7 @@
         <v>126918824</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3844,10 +3844,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912716</v>
+        <v>126912776</v>
       </c>
       <c r="B34" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672745</v>
+        <v>672932</v>
       </c>
       <c r="R34" t="n">
-        <v>7091092</v>
+        <v>7090808</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912776</v>
+        <v>126912716</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3952,21 +3952,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3976,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672932</v>
+        <v>672745</v>
       </c>
       <c r="R35" t="n">
-        <v>7090808</v>
+        <v>7091092</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919057</v>
+        <v>126919054</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672730</v>
+        <v>672705</v>
       </c>
       <c r="R36" t="n">
-        <v>7091091</v>
+        <v>7091127</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912877</v>
+        <v>126918826</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672754</v>
+        <v>672744</v>
       </c>
       <c r="R37" t="n">
-        <v>7091099</v>
+        <v>7091079</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,22 +4224,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126918826</v>
+        <v>126912877</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672744</v>
+        <v>672754</v>
       </c>
       <c r="R38" t="n">
-        <v>7091079</v>
+        <v>7091099</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4321,26 +4325,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126919051</v>
+        <v>126912774</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672702</v>
+        <v>672889</v>
       </c>
       <c r="R39" t="n">
-        <v>7091061</v>
+        <v>7090793</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,26 +4422,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919054</v>
+        <v>126919057</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,10 +4469,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672705</v>
+        <v>672730</v>
       </c>
       <c r="R40" t="n">
-        <v>7091127</v>
+        <v>7091091</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4539,10 +4535,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126912774</v>
+        <v>126919051</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4574,10 +4570,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672889</v>
+        <v>672702</v>
       </c>
       <c r="R41" t="n">
-        <v>7090793</v>
+        <v>7091061</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4624,44 +4620,48 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912927</v>
+        <v>126912865</v>
       </c>
       <c r="B42" t="n">
-        <v>92620</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672768</v>
+        <v>672783</v>
       </c>
       <c r="R42" t="n">
-        <v>7091045</v>
+        <v>7091147</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4733,10 +4733,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126913218</v>
+        <v>126912887</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672656</v>
+        <v>672750</v>
       </c>
       <c r="R43" t="n">
-        <v>7091011</v>
+        <v>7091052</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,26 +4818,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126918820</v>
+        <v>126913218</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4869,10 +4865,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672755</v>
+        <v>672656</v>
       </c>
       <c r="R44" t="n">
-        <v>7091121</v>
+        <v>7091011</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4919,12 +4915,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
@@ -4935,10 +4931,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126912887</v>
+        <v>126918820</v>
       </c>
       <c r="B45" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4970,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672750</v>
+        <v>672755</v>
       </c>
       <c r="R45" t="n">
-        <v>7091052</v>
+        <v>7091121</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5020,44 +5016,48 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919016</v>
+        <v>126912927</v>
       </c>
       <c r="B46" t="n">
-        <v>57483</v>
+        <v>92622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102976</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5067,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672887</v>
+        <v>672768</v>
       </c>
       <c r="R46" t="n">
-        <v>7090802</v>
+        <v>7091045</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,48 +5117,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126912865</v>
+        <v>126919016</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>57485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5168,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672783</v>
+        <v>672887</v>
       </c>
       <c r="R47" t="n">
-        <v>7091147</v>
+        <v>7090802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5218,22 +5214,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>126919050</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>126912713</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         <v>126912762</v>
       </c>
       <c r="B50" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>126919079</v>
       </c>
       <c r="B51" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>126912718</v>
       </c>
       <c r="B53" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912879</v>
+        <v>126912723</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>91254</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672751</v>
+        <v>672755</v>
       </c>
       <c r="R54" t="n">
-        <v>7091095</v>
+        <v>7091097</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5921,10 +5921,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912723</v>
+        <v>126912879</v>
       </c>
       <c r="B55" t="n">
-        <v>91252</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,21 +5932,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672755</v>
+        <v>672751</v>
       </c>
       <c r="R55" t="n">
-        <v>7091097</v>
+        <v>7091095</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6018,10 +6018,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126913223</v>
+        <v>126912868</v>
       </c>
       <c r="B56" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6029,21 +6029,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6053,10 +6053,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672862</v>
+        <v>672779</v>
       </c>
       <c r="R56" t="n">
-        <v>7090889</v>
+        <v>7091147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6103,26 +6103,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126919060</v>
+        <v>126913223</v>
       </c>
       <c r="B57" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6130,21 +6126,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6154,10 +6150,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672791</v>
+        <v>672862</v>
       </c>
       <c r="R57" t="n">
-        <v>7091150</v>
+        <v>7090889</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6204,12 +6200,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
@@ -6220,10 +6216,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912868</v>
+        <v>126919060</v>
       </c>
       <c r="B58" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6255,10 +6251,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672779</v>
+        <v>672791</v>
       </c>
       <c r="R58" t="n">
-        <v>7091147</v>
+        <v>7091150</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6305,22 +6301,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
         <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126912884</v>
       </c>
       <c r="B61" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672746</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7091051</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,26 +6605,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>126912892</v>
       </c>
       <c r="B62" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6718,10 +6714,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912884</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672746</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7091051</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,22 +6799,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126917430</v>
       </c>
       <c r="B64" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>126917438</v>
       </c>
       <c r="B65" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126917439</v>
       </c>
       <c r="B66" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7135,37 +7135,38 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B67" t="n">
-        <v>79018</v>
+        <v>56855</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7173,10 +7174,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R67" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7211,13 +7212,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7240,38 +7245,37 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B68" t="n">
-        <v>56853</v>
+        <v>79020</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7279,10 +7283,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R68" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7317,17 +7321,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7353,7 +7353,7 @@
         <v>126917436</v>
       </c>
       <c r="B69" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>126917440</v>
       </c>
       <c r="B70" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>126917434</v>
       </c>
       <c r="B71" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>126917441</v>
       </c>
       <c r="B72" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>126917444</v>
       </c>
       <c r="B73" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>126917442</v>
       </c>
       <c r="B74" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7984,32 +7984,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917443</v>
+        <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>79018</v>
+        <v>91593</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>65</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8022,10 +8022,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672714</v>
+        <v>672713</v>
       </c>
       <c r="R75" t="n">
-        <v>7091092</v>
+        <v>7090990</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8089,32 +8089,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917447</v>
+        <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>91591</v>
+        <v>79020</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8127,10 +8127,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672713</v>
+        <v>672714</v>
       </c>
       <c r="R76" t="n">
-        <v>7090990</v>
+        <v>7091092</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8197,7 +8197,7 @@
         <v>126917432</v>
       </c>
       <c r="B77" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>126913591</v>
       </c>
       <c r="B78" t="n">
-        <v>78685</v>
+        <v>78687</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8610,7 +8610,7 @@
         <v>126913586</v>
       </c>
       <c r="B81" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>126913587</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>126913589</v>
       </c>
       <c r="B83" t="n">
-        <v>79042</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B84" t="n">
-        <v>79050</v>
+        <v>79020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R84" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R85" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9115,7 +9115,7 @@
         <v>126913584</v>
       </c>
       <c r="B86" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>126913585</v>
       </c>
       <c r="B87" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>126913593</v>
       </c>
       <c r="B88" t="n">
-        <v>79050</v>
+        <v>79052</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126912928</v>
+        <v>126918815</v>
       </c>
       <c r="B2" t="n">
-        <v>92622</v>
+        <v>78778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672944</v>
+        <v>672767</v>
       </c>
       <c r="R2" t="n">
-        <v>7090839</v>
+        <v>7090991</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,15 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -963,39 +967,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B5" t="n">
-        <v>78778</v>
+        <v>92622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1005,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R5" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1055,48 +1059,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126913222</v>
+        <v>126919058</v>
       </c>
       <c r="B6" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672883</v>
+        <v>672737</v>
       </c>
       <c r="R6" t="n">
-        <v>7090921</v>
+        <v>7091090</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1262,39 +1262,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126919058</v>
+        <v>126913222</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672737</v>
+        <v>672883</v>
       </c>
       <c r="R8" t="n">
-        <v>7091090</v>
+        <v>7090921</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,12 +1354,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912932</v>
+        <v>126912715</v>
       </c>
       <c r="B9" t="n">
-        <v>78687</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672755</v>
+        <v>672914</v>
       </c>
       <c r="R9" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126919056</v>
+        <v>126912875</v>
       </c>
       <c r="B10" t="n">
         <v>79020</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672702</v>
+        <v>672751</v>
       </c>
       <c r="R10" t="n">
-        <v>7091127</v>
+        <v>7091113</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,26 +1552,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126912715</v>
+        <v>126918821</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1603,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672914</v>
+        <v>672752</v>
       </c>
       <c r="R11" t="n">
-        <v>7090807</v>
+        <v>7091197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1653,19 +1649,23 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126912875</v>
+        <v>126919053</v>
       </c>
       <c r="B12" t="n">
         <v>79020</v>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672751</v>
+        <v>672698</v>
       </c>
       <c r="R12" t="n">
-        <v>7091113</v>
+        <v>7091075</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,22 +1750,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912726</v>
+        <v>126912932</v>
       </c>
       <c r="B13" t="n">
-        <v>79609</v>
+        <v>78687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1773,21 +1777,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1797,10 +1801,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672750</v>
+        <v>672755</v>
       </c>
       <c r="R13" t="n">
-        <v>7091112</v>
+        <v>7091113</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,7 +1863,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126918821</v>
+        <v>126919056</v>
       </c>
       <c r="B14" t="n">
         <v>79020</v>
@@ -1894,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672752</v>
+        <v>672702</v>
       </c>
       <c r="R14" t="n">
-        <v>7091197</v>
+        <v>7091127</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,12 +1948,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1960,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126919053</v>
+        <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1995,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672698</v>
+        <v>672750</v>
       </c>
       <c r="R15" t="n">
-        <v>7091075</v>
+        <v>7091112</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,19 +2049,15 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Philipp Weiss, Cajsa Björkén, Liam Sebestyén</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3145,14 +3145,14 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126912860</v>
+        <v>126918831</v>
       </c>
       <c r="B27" t="n">
         <v>79020</v>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672791</v>
+        <v>672756</v>
       </c>
       <c r="R27" t="n">
-        <v>7091154</v>
+        <v>7090952</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,19 +3237,23 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126918831</v>
+        <v>126912860</v>
       </c>
       <c r="B28" t="n">
         <v>79020</v>
@@ -3284,10 +3288,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672756</v>
+        <v>672791</v>
       </c>
       <c r="R28" t="n">
-        <v>7090952</v>
+        <v>7091154</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3334,26 +3338,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912717</v>
+        <v>126912933</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3361,21 +3361,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3385,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672735</v>
+        <v>672871</v>
       </c>
       <c r="R29" t="n">
-        <v>7091083</v>
+        <v>7090905</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,10 +3447,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912944</v>
+        <v>126912749</v>
       </c>
       <c r="B30" t="n">
-        <v>78426</v>
+        <v>92815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3458,21 +3458,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6437</v>
+        <v>2079</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3482,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672756</v>
+        <v>672946</v>
       </c>
       <c r="R30" t="n">
-        <v>7091093</v>
+        <v>7090821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,11 +3518,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3549,10 +3544,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912933</v>
+        <v>126912944</v>
       </c>
       <c r="B31" t="n">
-        <v>78687</v>
+        <v>78426</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3560,21 +3555,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3584,10 +3579,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672871</v>
+        <v>672756</v>
       </c>
       <c r="R31" t="n">
-        <v>7090905</v>
+        <v>7091093</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,6 +3615,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,10 +3646,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912749</v>
+        <v>126912717</v>
       </c>
       <c r="B32" t="n">
-        <v>92815</v>
+        <v>79638</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3657,21 +3657,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3681,10 +3681,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672946</v>
+        <v>672735</v>
       </c>
       <c r="R32" t="n">
-        <v>7090821</v>
+        <v>7091083</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -4038,7 +4038,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919054</v>
+        <v>126919057</v>
       </c>
       <c r="B36" t="n">
         <v>79020</v>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672705</v>
+        <v>672730</v>
       </c>
       <c r="R36" t="n">
-        <v>7091127</v>
+        <v>7091091</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,7 +4139,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126918826</v>
+        <v>126912774</v>
       </c>
       <c r="B37" t="n">
         <v>79020</v>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672744</v>
+        <v>672889</v>
       </c>
       <c r="R37" t="n">
-        <v>7091079</v>
+        <v>7090793</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,23 +4224,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126912877</v>
+        <v>126919054</v>
       </c>
       <c r="B38" t="n">
         <v>79020</v>
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672754</v>
+        <v>672705</v>
       </c>
       <c r="R38" t="n">
-        <v>7091099</v>
+        <v>7091127</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,19 +4321,23 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126912774</v>
+        <v>126918826</v>
       </c>
       <c r="B39" t="n">
         <v>79020</v>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672889</v>
+        <v>672744</v>
       </c>
       <c r="R39" t="n">
-        <v>7090793</v>
+        <v>7091079</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,19 +4422,23 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr"/>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126919057</v>
+        <v>126912877</v>
       </c>
       <c r="B40" t="n">
         <v>79020</v>
@@ -4469,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672730</v>
+        <v>672754</v>
       </c>
       <c r="R40" t="n">
-        <v>7091091</v>
+        <v>7091099</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4519,19 +4523,15 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4636,32 +4636,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912865</v>
+        <v>126912927</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>92622</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4671,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672783</v>
+        <v>672768</v>
       </c>
       <c r="R42" t="n">
-        <v>7091147</v>
+        <v>7091045</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4733,7 +4733,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912887</v>
+        <v>126912865</v>
       </c>
       <c r="B43" t="n">
         <v>79020</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672750</v>
+        <v>672783</v>
       </c>
       <c r="R43" t="n">
-        <v>7091052</v>
+        <v>7091147</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,14 +4823,14 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126913218</v>
+        <v>126912887</v>
       </c>
       <c r="B44" t="n">
         <v>79020</v>
@@ -4865,10 +4865,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672656</v>
+        <v>672750</v>
       </c>
       <c r="R44" t="n">
-        <v>7091011</v>
+        <v>7091052</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4915,23 +4915,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126918820</v>
+        <v>126913218</v>
       </c>
       <c r="B45" t="n">
         <v>79020</v>
@@ -4966,10 +4962,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672755</v>
+        <v>672656</v>
       </c>
       <c r="R45" t="n">
-        <v>7091121</v>
+        <v>7091011</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5016,12 +5012,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -5032,32 +5028,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126912927</v>
+        <v>126919016</v>
       </c>
       <c r="B46" t="n">
-        <v>92622</v>
+        <v>57485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>102976</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5067,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672768</v>
+        <v>672887</v>
       </c>
       <c r="R46" t="n">
-        <v>7091045</v>
+        <v>7090802</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5117,44 +5113,48 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126919016</v>
+        <v>126918820</v>
       </c>
       <c r="B47" t="n">
-        <v>57485</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672887</v>
+        <v>672755</v>
       </c>
       <c r="R47" t="n">
-        <v>7090802</v>
+        <v>7091121</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,12 +5214,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B49" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R49" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,22 +5416,26 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B50" t="n">
-        <v>91350</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5439,21 +5443,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5463,10 +5467,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R50" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5525,32 +5529,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B51" t="n">
-        <v>92622</v>
+        <v>91350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5560,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R51" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5610,19 +5614,15 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126912879</v>
+        <v>126913223</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,21 +5932,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672751</v>
+        <v>672862</v>
       </c>
       <c r="R55" t="n">
-        <v>7091095</v>
+        <v>7090889</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,19 +6006,23 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126912868</v>
+        <v>126919060</v>
       </c>
       <c r="B56" t="n">
         <v>79020</v>
@@ -6053,10 +6057,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672779</v>
+        <v>672791</v>
       </c>
       <c r="R56" t="n">
-        <v>7091147</v>
+        <v>7091150</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6103,22 +6107,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126913223</v>
+        <v>126912879</v>
       </c>
       <c r="B57" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6126,21 +6134,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6150,10 +6158,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672862</v>
+        <v>672751</v>
       </c>
       <c r="R57" t="n">
-        <v>7090889</v>
+        <v>7091095</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6200,23 +6208,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126919060</v>
+        <v>126912868</v>
       </c>
       <c r="B58" t="n">
         <v>79020</v>
@@ -6251,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672791</v>
+        <v>672779</v>
       </c>
       <c r="R58" t="n">
-        <v>7091150</v>
+        <v>7091147</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6301,19 +6305,15 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6520,10 +6520,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126912884</v>
+        <v>126913217</v>
       </c>
       <c r="B61" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672746</v>
+        <v>672643</v>
       </c>
       <c r="R61" t="n">
-        <v>7091051</v>
+        <v>7091013</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,19 +6605,23 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912892</v>
+        <v>126912884</v>
       </c>
       <c r="B62" t="n">
         <v>79020</v>
@@ -6652,10 +6656,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672787</v>
+        <v>672746</v>
       </c>
       <c r="R62" t="n">
-        <v>7090995</v>
+        <v>7091051</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6707,17 +6711,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126913217</v>
+        <v>126912892</v>
       </c>
       <c r="B63" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6725,21 +6729,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6749,10 +6753,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672643</v>
+        <v>672787</v>
       </c>
       <c r="R63" t="n">
-        <v>7091013</v>
+        <v>7090995</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6799,19 +6803,15 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7135,38 +7135,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917433</v>
+        <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7174,10 +7173,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672876</v>
+        <v>672706</v>
       </c>
       <c r="R67" t="n">
-        <v>7090878</v>
+        <v>7090986</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7212,17 +7211,13 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7245,37 +7240,38 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917445</v>
+        <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -7283,10 +7279,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672706</v>
+        <v>672876</v>
       </c>
       <c r="R68" t="n">
-        <v>7090986</v>
+        <v>7090878</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7321,13 +7317,17 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917434</v>
+        <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>79020</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7571,31 +7571,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7603,10 +7598,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672734</v>
+        <v>672705</v>
       </c>
       <c r="R71" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7647,6 +7642,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7669,10 +7665,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917441</v>
+        <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>79020</v>
+        <v>57823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7680,26 +7676,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7707,10 +7708,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672705</v>
+        <v>672734</v>
       </c>
       <c r="R72" t="n">
-        <v>7091153</v>
+        <v>7091231</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -7751,7 +7752,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R79" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B80" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R80" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,10 +8910,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913582</v>
+        <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8921,21 +8921,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8945,10 +8945,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672738</v>
+        <v>672865</v>
       </c>
       <c r="R84" t="n">
-        <v>7091189</v>
+        <v>7090849</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9011,10 +9011,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913588</v>
+        <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79052</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9022,21 +9022,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9046,10 +9046,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672865</v>
+        <v>672738</v>
       </c>
       <c r="R85" t="n">
-        <v>7090849</v>
+        <v>7091189</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B79" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R79" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B80" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R80" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918815</v>
+        <v>126912928</v>
       </c>
       <c r="B2" t="n">
-        <v>78778</v>
+        <v>92609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672767</v>
+        <v>672944</v>
       </c>
       <c r="R2" t="n">
-        <v>7090991</v>
+        <v>7090839</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,26 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918830</v>
+        <v>126918815</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>78769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672770</v>
+        <v>672767</v>
       </c>
       <c r="R3" t="n">
-        <v>7090981</v>
+        <v>7090991</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +876,7 @@
         <v>126912889</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,39 +963,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126912928</v>
+        <v>126918830</v>
       </c>
       <c r="B5" t="n">
-        <v>92622</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672944</v>
+        <v>672770</v>
       </c>
       <c r="R5" t="n">
-        <v>7090839</v>
+        <v>7090981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,44 +1055,48 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126919058</v>
+        <v>126913222</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>56849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672737</v>
+        <v>672883</v>
       </c>
       <c r="R6" t="n">
-        <v>7091090</v>
+        <v>7090921</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,12 +1156,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1175,7 +1175,7 @@
         <v>126912873</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,39 +1262,39 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126913222</v>
+        <v>126919058</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672883</v>
+        <v>672737</v>
       </c>
       <c r="R8" t="n">
-        <v>7090921</v>
+        <v>7091090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,12 +1354,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912715</v>
+        <v>126912932</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>78678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672914</v>
+        <v>672755</v>
       </c>
       <c r="R9" t="n">
-        <v>7090807</v>
+        <v>7091113</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,17 +1460,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126912715</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672914</v>
       </c>
       <c r="R10" t="n">
-        <v>7091113</v>
+        <v>7090807</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1557,17 +1557,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126919053</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672698</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7091075</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,12 +1649,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919053</v>
+        <v>126919056</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672698</v>
+        <v>672702</v>
       </c>
       <c r="R12" t="n">
-        <v>7091075</v>
+        <v>7091127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1766,10 +1766,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912932</v>
+        <v>126912875</v>
       </c>
       <c r="B13" t="n">
-        <v>78687</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1801,7 +1801,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672755</v>
+        <v>672751</v>
       </c>
       <c r="R13" t="n">
         <v>7091113</v>
@@ -1863,10 +1863,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919056</v>
+        <v>126918821</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1898,10 +1898,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672702</v>
+        <v>672752</v>
       </c>
       <c r="R14" t="n">
-        <v>7091127</v>
+        <v>7091197</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,12 +1948,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1967,7 +1967,7 @@
         <v>126912726</v>
       </c>
       <c r="B15" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912935</v>
+        <v>126918827</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2072,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672815</v>
+        <v>672753</v>
       </c>
       <c r="R16" t="n">
-        <v>7090911</v>
+        <v>7091016</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,22 +2146,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
         <v>126912882</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918827</v>
+        <v>126912935</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672753</v>
+        <v>672815</v>
       </c>
       <c r="R18" t="n">
-        <v>7091016</v>
+        <v>7090911</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,26 +2344,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>126913219</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918825</v>
+        <v>126918828</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672764</v>
+        <v>672757</v>
       </c>
       <c r="R20" t="n">
-        <v>7091153</v>
+        <v>7091027</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918828</v>
+        <v>126918825</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672757</v>
+        <v>672764</v>
       </c>
       <c r="R21" t="n">
-        <v>7091027</v>
+        <v>7091153</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2659,10 +2659,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912930</v>
+        <v>126912862</v>
       </c>
       <c r="B22" t="n">
-        <v>78687</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2670,21 +2670,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2694,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672825</v>
+        <v>672787</v>
       </c>
       <c r="R22" t="n">
-        <v>7090914</v>
+        <v>7091154</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,10 +2756,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912862</v>
+        <v>126912930</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>78678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2767,21 +2767,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2791,10 +2791,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672787</v>
+        <v>672825</v>
       </c>
       <c r="R23" t="n">
-        <v>7091154</v>
+        <v>7090914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2853,10 +2853,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126919059</v>
+        <v>126913216</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672732</v>
+        <v>672804</v>
       </c>
       <c r="R24" t="n">
-        <v>7091173</v>
+        <v>7091051</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,12 +2938,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126913216</v>
+        <v>126919059</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672804</v>
+        <v>672732</v>
       </c>
       <c r="R25" t="n">
-        <v>7091051</v>
+        <v>7091173</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,12 +3039,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
@@ -3058,7 +3058,7 @@
         <v>126912870</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3145,17 +3145,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918831</v>
+        <v>126912860</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672756</v>
+        <v>672791</v>
       </c>
       <c r="R27" t="n">
-        <v>7090952</v>
+        <v>7091154</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,26 +3237,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912860</v>
+        <v>126918831</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3288,10 +3284,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672791</v>
+        <v>672756</v>
       </c>
       <c r="R28" t="n">
-        <v>7091154</v>
+        <v>7090952</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3338,22 +3334,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
         <v>126912933</v>
       </c>
       <c r="B29" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3450,7 +3450,7 @@
         <v>126912749</v>
       </c>
       <c r="B30" t="n">
-        <v>92815</v>
+        <v>92802</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3544,10 +3544,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912944</v>
+        <v>126912717</v>
       </c>
       <c r="B31" t="n">
-        <v>78426</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3555,21 +3555,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3579,10 +3579,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672756</v>
+        <v>672735</v>
       </c>
       <c r="R31" t="n">
-        <v>7091093</v>
+        <v>7091083</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,11 +3615,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,10 +3641,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912717</v>
+        <v>126912944</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>78417</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3657,21 +3652,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3681,10 +3676,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672735</v>
+        <v>672756</v>
       </c>
       <c r="R32" t="n">
-        <v>7091083</v>
+        <v>7091093</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,6 +3712,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3746,7 +3746,7 @@
         <v>126918824</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
@@ -3847,7 +3847,7 @@
         <v>126912776</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3944,7 +3944,7 @@
         <v>126912716</v>
       </c>
       <c r="B35" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4038,10 +4038,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919057</v>
+        <v>126919054</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4073,10 +4073,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672730</v>
+        <v>672705</v>
       </c>
       <c r="R36" t="n">
-        <v>7091091</v>
+        <v>7091127</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4139,10 +4139,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912774</v>
+        <v>126919057</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4174,10 +4174,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672889</v>
+        <v>672730</v>
       </c>
       <c r="R37" t="n">
-        <v>7090793</v>
+        <v>7091091</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4224,22 +4224,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919054</v>
+        <v>126912877</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4271,10 +4275,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672705</v>
+        <v>672754</v>
       </c>
       <c r="R38" t="n">
-        <v>7091127</v>
+        <v>7091099</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4321,26 +4325,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
         <v>126918826</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
@@ -4438,10 +4438,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126912877</v>
+        <v>126912774</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672754</v>
+        <v>672889</v>
       </c>
       <c r="R40" t="n">
-        <v>7091099</v>
+        <v>7090793</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4538,7 +4538,7 @@
         <v>126919051</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>126912927</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>92609</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4726,17 +4726,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912865</v>
+        <v>126918820</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672783</v>
+        <v>672755</v>
       </c>
       <c r="R43" t="n">
-        <v>7091147</v>
+        <v>7091121</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4818,22 +4818,26 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr"/>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>126912887</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4920,7 +4924,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -4930,7 +4934,7 @@
         <v>126913218</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5028,32 +5032,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919016</v>
+        <v>126912865</v>
       </c>
       <c r="B46" t="n">
-        <v>57485</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5067,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672887</v>
+        <v>672783</v>
       </c>
       <c r="R46" t="n">
-        <v>7090802</v>
+        <v>7091147</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5113,48 +5117,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126918820</v>
+        <v>126919016</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>57479</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>102976</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5164,10 +5164,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672755</v>
+        <v>672887</v>
       </c>
       <c r="R47" t="n">
-        <v>7091121</v>
+        <v>7090802</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,12 +5214,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -5233,7 +5233,7 @@
         <v>126919050</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5331,32 +5331,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126912762</v>
       </c>
       <c r="B49" t="n">
-        <v>92622</v>
+        <v>91337</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672743</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091094</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,48 +5416,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912713</v>
+        <v>126919079</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>92609</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5463,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672780</v>
+        <v>672953</v>
       </c>
       <c r="R50" t="n">
-        <v>7091043</v>
+        <v>7090819</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,22 +5513,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126912713</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>79629</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5540,21 +5540,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5564,10 +5564,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672780</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7091043</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5629,7 +5629,7 @@
         <v>126919049</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         <v>126912718</v>
       </c>
       <c r="B53" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5824,10 +5824,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912723</v>
+        <v>126913223</v>
       </c>
       <c r="B54" t="n">
-        <v>91254</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5835,21 +5835,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672755</v>
+        <v>672862</v>
       </c>
       <c r="R54" t="n">
-        <v>7091097</v>
+        <v>7090889</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,22 +5909,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913223</v>
+        <v>126919060</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5932,21 +5936,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5956,10 +5960,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672862</v>
+        <v>672791</v>
       </c>
       <c r="R55" t="n">
-        <v>7090889</v>
+        <v>7091150</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,12 +6010,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6022,10 +6026,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919060</v>
+        <v>126912868</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6057,10 +6061,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672791</v>
+        <v>672779</v>
       </c>
       <c r="R56" t="n">
-        <v>7091150</v>
+        <v>7091147</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6107,26 +6111,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
         <v>126912879</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6213,17 +6213,17 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912868</v>
+        <v>126912723</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>91241</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6231,21 +6231,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6255,10 +6255,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672779</v>
+        <v>672755</v>
       </c>
       <c r="R58" t="n">
-        <v>7091147</v>
+        <v>7091097</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6320,7 +6320,7 @@
         <v>126919018</v>
       </c>
       <c r="B59" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         <v>126912934</v>
       </c>
       <c r="B60" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6513,17 +6513,17 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126912892</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>79011</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6531,21 +6531,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6555,10 +6555,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672787</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7090995</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6605,26 +6605,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
         <v>126912884</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6711,17 +6707,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912892</v>
+        <v>126913217</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6729,21 +6725,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672787</v>
+        <v>672643</v>
       </c>
       <c r="R63" t="n">
-        <v>7090995</v>
+        <v>7091013</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6803,22 +6799,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
         <v>126917430</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>126917438</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>126917439</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>126917445</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7243,7 +7243,7 @@
         <v>126917433</v>
       </c>
       <c r="B68" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>126917436</v>
       </c>
       <c r="B69" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         <v>126917440</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>126917441</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>126917434</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>57817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
         <v>126917444</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>126917442</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         <v>126917447</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>91580</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>126917443</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8197,7 +8197,7 @@
         <v>126917432</v>
       </c>
       <c r="B77" t="n">
-        <v>56855</v>
+        <v>56849</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8307,7 +8307,7 @@
         <v>126913591</v>
       </c>
       <c r="B78" t="n">
-        <v>78687</v>
+        <v>78678</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8405,10 +8405,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126913583</v>
       </c>
       <c r="B79" t="n">
-        <v>79638</v>
+        <v>79011</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8416,21 +8416,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8440,10 +8440,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672728</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091029</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8506,10 +8506,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126913592</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8517,21 +8517,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8541,10 +8541,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672892</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7090833</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8610,7 +8610,7 @@
         <v>126913586</v>
       </c>
       <c r="B81" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         <v>126913587</v>
       </c>
       <c r="B82" t="n">
-        <v>79609</v>
+        <v>79600</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8812,7 +8812,7 @@
         <v>126913589</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8913,7 +8913,7 @@
         <v>126913588</v>
       </c>
       <c r="B84" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>126913582</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>126913584</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>126913585</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>126913593</v>
       </c>
       <c r="B88" t="n">
-        <v>79052</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AY114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126918815</v>
+        <v>126917447</v>
       </c>
       <c r="B2" t="n">
-        <v>78778</v>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672767</v>
+        <v>672713</v>
       </c>
       <c r="R2" t="n">
-        <v>7090991</v>
+        <v>7090990</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,18 +757,19 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -776,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126918830</v>
+        <v>126912725</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672770</v>
+        <v>672797</v>
       </c>
       <c r="R3" t="n">
-        <v>7090981</v>
+        <v>7091173</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,26 +865,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126912889</v>
+        <v>126913223</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672798</v>
+        <v>672862</v>
       </c>
       <c r="R4" t="n">
-        <v>7091015</v>
+        <v>7090889</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,57 +962,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126912928</v>
+        <v>126913588</v>
       </c>
       <c r="B5" t="n">
-        <v>92622</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672944</v>
+        <v>672865</v>
       </c>
       <c r="R5" t="n">
-        <v>7090839</v>
+        <v>7090849</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,22 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126919058</v>
+        <v>126913593</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1090,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>672737</v>
+        <v>672910</v>
       </c>
       <c r="R6" t="n">
-        <v>7091090</v>
+        <v>7090821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1156,12 +1164,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1172,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126912873</v>
+        <v>126917430</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,37 +1191,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>672756</v>
+        <v>672707</v>
       </c>
       <c r="R7" t="n">
-        <v>7091126</v>
+        <v>7091108</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1251,50 +1262,55 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126913222</v>
+        <v>126912930</v>
       </c>
       <c r="B8" t="n">
-        <v>56855</v>
+        <v>78993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1304,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>672883</v>
+        <v>672825</v>
       </c>
       <c r="R8" t="n">
-        <v>7090921</v>
+        <v>7090914</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,26 +1370,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126912715</v>
+        <v>126912931</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>78993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1393,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>672914</v>
+        <v>672963</v>
       </c>
       <c r="R9" t="n">
-        <v>7090807</v>
+        <v>7090832</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1479,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126912875</v>
+        <v>126912932</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1490,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,7 +1514,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>672751</v>
+        <v>672755</v>
       </c>
       <c r="R10" t="n">
         <v>7091113</v>
@@ -1557,17 +1569,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126918821</v>
+        <v>126912933</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1587,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1611,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>672752</v>
+        <v>672871</v>
       </c>
       <c r="R11" t="n">
-        <v>7091197</v>
+        <v>7090905</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,26 +1661,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126919053</v>
+        <v>126912934</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,21 +1684,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1700,10 +1708,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>672698</v>
+        <v>672873</v>
       </c>
       <c r="R12" t="n">
-        <v>7091075</v>
+        <v>7090916</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,26 +1758,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126912932</v>
+        <v>126912935</v>
       </c>
       <c r="B13" t="n">
-        <v>78687</v>
+        <v>78993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1801,10 +1805,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>672755</v>
+        <v>672815</v>
       </c>
       <c r="R13" t="n">
-        <v>7091113</v>
+        <v>7090911</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,10 +1867,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126919056</v>
+        <v>126913591</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,34 +1878,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>672702</v>
+        <v>672892</v>
       </c>
       <c r="R14" t="n">
-        <v>7091127</v>
+        <v>7090833</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,12 +1952,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -1964,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126912726</v>
+        <v>126912749</v>
       </c>
       <c r="B15" t="n">
-        <v>79609</v>
+        <v>91962</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>672750</v>
+        <v>672946</v>
       </c>
       <c r="R15" t="n">
-        <v>7091112</v>
+        <v>7090821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,10 +2065,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126912935</v>
+        <v>126912723</v>
       </c>
       <c r="B16" t="n">
-        <v>78687</v>
+        <v>91831</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2072,21 +2076,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2096,10 +2100,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>672815</v>
+        <v>672755</v>
       </c>
       <c r="R16" t="n">
-        <v>7090911</v>
+        <v>7091097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,10 +2162,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126912882</v>
+        <v>126912927</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2169,21 +2173,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2193,10 +2197,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>672738</v>
+        <v>672768</v>
       </c>
       <c r="R17" t="n">
-        <v>7091066</v>
+        <v>7091045</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,17 +2252,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126918827</v>
+        <v>126912928</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2266,21 +2270,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2290,10 +2294,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>672753</v>
+        <v>672944</v>
       </c>
       <c r="R18" t="n">
-        <v>7091016</v>
+        <v>7090839</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,26 +2344,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126913219</v>
+        <v>126919079</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2367,21 +2367,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>672627</v>
+        <v>672953</v>
       </c>
       <c r="R19" t="n">
-        <v>7091008</v>
+        <v>7090819</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,12 +2441,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2457,14 +2457,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126918825</v>
+        <v>80865059</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2492,10 +2492,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>672764</v>
+        <v>672802</v>
       </c>
       <c r="R20" t="n">
-        <v>7091153</v>
+        <v>7091215</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,12 +2522,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2019-08-07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2542,30 +2542,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Julia Pettersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Julia Pettersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126918828</v>
+        <v>126912774</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2593,10 +2589,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>672757</v>
+        <v>672889</v>
       </c>
       <c r="R21" t="n">
-        <v>7091027</v>
+        <v>7090793</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2643,48 +2639,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126912930</v>
+        <v>126912776</v>
       </c>
       <c r="B22" t="n">
-        <v>78687</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2694,10 +2686,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>672825</v>
+        <v>672932</v>
       </c>
       <c r="R22" t="n">
-        <v>7090914</v>
+        <v>7090808</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2756,14 +2748,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126912862</v>
+        <v>126912840</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2791,10 +2783,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>672787</v>
+        <v>672801</v>
       </c>
       <c r="R23" t="n">
-        <v>7091154</v>
+        <v>7091213</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,21 +2838,21 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126919059</v>
+        <v>126912844</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2888,10 +2880,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>672732</v>
+        <v>672791</v>
       </c>
       <c r="R24" t="n">
-        <v>7091173</v>
+        <v>7091209</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2938,30 +2930,26 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126913216</v>
+        <v>126912847</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2989,10 +2977,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>672804</v>
+        <v>672789</v>
       </c>
       <c r="R25" t="n">
-        <v>7091051</v>
+        <v>7091197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3039,30 +3027,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126912870</v>
+        <v>126912851</v>
       </c>
       <c r="B26" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3090,10 +3074,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>672767</v>
+        <v>672788</v>
       </c>
       <c r="R26" t="n">
-        <v>7091137</v>
+        <v>7091187</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3145,21 +3129,21 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126918831</v>
+        <v>126912853</v>
       </c>
       <c r="B27" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3187,10 +3171,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>672756</v>
+        <v>672792</v>
       </c>
       <c r="R27" t="n">
-        <v>7090952</v>
+        <v>7091184</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,30 +3221,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126912860</v>
+        <v>126912855</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3288,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>672791</v>
+        <v>672794</v>
       </c>
       <c r="R28" t="n">
-        <v>7091154</v>
+        <v>7091175</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3343,39 +3323,39 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126912933</v>
+        <v>126912858</v>
       </c>
       <c r="B29" t="n">
-        <v>78687</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3385,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>672871</v>
+        <v>672795</v>
       </c>
       <c r="R29" t="n">
-        <v>7090905</v>
+        <v>7091173</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3447,32 +3427,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126912749</v>
+        <v>126912860</v>
       </c>
       <c r="B30" t="n">
-        <v>92815</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3482,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>672946</v>
+        <v>672791</v>
       </c>
       <c r="R30" t="n">
-        <v>7090821</v>
+        <v>7091154</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3544,32 +3524,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126912944</v>
+        <v>126912862</v>
       </c>
       <c r="B31" t="n">
-        <v>78426</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3579,10 +3559,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>672756</v>
+        <v>672787</v>
       </c>
       <c r="R31" t="n">
-        <v>7091093</v>
+        <v>7091154</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,11 +3595,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På torraka med 4 brandljud</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3646,32 +3621,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126912717</v>
+        <v>126912865</v>
       </c>
       <c r="B32" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3681,10 +3656,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>672735</v>
+        <v>672783</v>
       </c>
       <c r="R32" t="n">
-        <v>7091083</v>
+        <v>7091147</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3743,14 +3718,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126918824</v>
+        <v>126912868</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3778,10 +3753,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>672781</v>
+        <v>672779</v>
       </c>
       <c r="R33" t="n">
-        <v>7091162</v>
+        <v>7091147</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3828,30 +3803,26 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>126912776</v>
+        <v>126912870</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3879,10 +3850,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>672932</v>
+        <v>672767</v>
       </c>
       <c r="R34" t="n">
-        <v>7090808</v>
+        <v>7091137</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3941,32 +3912,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>126912716</v>
+        <v>126912873</v>
       </c>
       <c r="B35" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3976,10 +3947,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>672745</v>
+        <v>672756</v>
       </c>
       <c r="R35" t="n">
-        <v>7091092</v>
+        <v>7091126</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4038,14 +4009,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126919057</v>
+        <v>126912875</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4073,10 +4044,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>672730</v>
+        <v>672751</v>
       </c>
       <c r="R36" t="n">
-        <v>7091091</v>
+        <v>7091113</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4123,30 +4094,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126912774</v>
+        <v>126912877</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4174,10 +4141,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>672889</v>
+        <v>672754</v>
       </c>
       <c r="R37" t="n">
-        <v>7090793</v>
+        <v>7091099</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4236,14 +4203,14 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126919054</v>
+        <v>126912879</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4271,10 +4238,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>672705</v>
+        <v>672751</v>
       </c>
       <c r="R38" t="n">
-        <v>7091127</v>
+        <v>7091095</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4321,30 +4288,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>126918826</v>
+        <v>126912882</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4372,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>672744</v>
+        <v>672738</v>
       </c>
       <c r="R39" t="n">
-        <v>7091079</v>
+        <v>7091066</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4422,30 +4385,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>126912877</v>
+        <v>126912884</v>
       </c>
       <c r="B40" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4473,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>672754</v>
+        <v>672746</v>
       </c>
       <c r="R40" t="n">
-        <v>7091099</v>
+        <v>7091051</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4528,21 +4487,21 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>126919051</v>
+        <v>126912887</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4570,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>672702</v>
+        <v>672750</v>
       </c>
       <c r="R41" t="n">
-        <v>7091061</v>
+        <v>7091052</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4620,48 +4579,44 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126912927</v>
+        <v>126912889</v>
       </c>
       <c r="B42" t="n">
-        <v>92622</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4671,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>672768</v>
+        <v>672798</v>
       </c>
       <c r="R42" t="n">
-        <v>7091045</v>
+        <v>7091015</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4733,14 +4688,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126912865</v>
+        <v>126912892</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4768,10 +4723,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>672783</v>
+        <v>672787</v>
       </c>
       <c r="R43" t="n">
-        <v>7091147</v>
+        <v>7090995</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4823,21 +4778,21 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126912887</v>
+        <v>126912894</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4865,10 +4820,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>672750</v>
+        <v>672813</v>
       </c>
       <c r="R44" t="n">
-        <v>7091052</v>
+        <v>7090978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4920,21 +4875,21 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126913218</v>
+        <v>126912898</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -4962,10 +4917,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>672656</v>
+        <v>672804</v>
       </c>
       <c r="R45" t="n">
-        <v>7091011</v>
+        <v>7090880</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5012,48 +4967,44 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>126919016</v>
+        <v>126912901</v>
       </c>
       <c r="B46" t="n">
-        <v>57485</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>102976</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5063,10 +5014,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>672887</v>
+        <v>672805</v>
       </c>
       <c r="R46" t="n">
-        <v>7090802</v>
+        <v>7090886</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5113,30 +5064,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>126918820</v>
+        <v>126912903</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5164,10 +5111,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>672755</v>
+        <v>672791</v>
       </c>
       <c r="R47" t="n">
-        <v>7091121</v>
+        <v>7090883</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5214,30 +5161,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Philipp Weiss, Lars-Erik Nilsson, Alexandra Astafourova, Martin Axegård, Liam Sebestyén, Cajsa Björkén</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr">
-        <is>
-          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
-        </is>
-      </c>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>126919050</v>
+        <v>126913216</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5265,10 +5208,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>672719</v>
+        <v>672804</v>
       </c>
       <c r="R48" t="n">
-        <v>7091052</v>
+        <v>7091051</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5315,12 +5258,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -5331,32 +5274,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126919079</v>
+        <v>126913218</v>
       </c>
       <c r="B49" t="n">
-        <v>92622</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5366,10 +5309,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>672953</v>
+        <v>672656</v>
       </c>
       <c r="R49" t="n">
-        <v>7090819</v>
+        <v>7091011</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5416,12 +5359,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
@@ -5432,32 +5375,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>126912713</v>
+        <v>126913219</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5467,10 +5410,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>672780</v>
+        <v>672627</v>
       </c>
       <c r="R50" t="n">
-        <v>7091043</v>
+        <v>7091008</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5517,57 +5460,61 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>126912762</v>
+        <v>126913582</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>672743</v>
+        <v>672738</v>
       </c>
       <c r="R51" t="n">
-        <v>7091094</v>
+        <v>7091189</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5614,26 +5561,30 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>126919049</v>
+        <v>126913583</v>
       </c>
       <c r="B52" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5657,14 +5608,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>672651</v>
+        <v>672728</v>
       </c>
       <c r="R52" t="n">
-        <v>7091012</v>
+        <v>7091029</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5711,12 +5662,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -5727,45 +5678,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126912718</v>
+        <v>126913584</v>
       </c>
       <c r="B53" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>672824</v>
+        <v>672813</v>
       </c>
       <c r="R53" t="n">
-        <v>7090912</v>
+        <v>7091003</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5812,57 +5763,61 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126912723</v>
+        <v>126913585</v>
       </c>
       <c r="B54" t="n">
-        <v>91254</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>3242</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>672755</v>
+        <v>672813</v>
       </c>
       <c r="R54" t="n">
-        <v>7091097</v>
+        <v>7090992</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5909,57 +5864,61 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126913223</v>
+        <v>126913590</v>
       </c>
       <c r="B55" t="n">
-        <v>79052</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lappberget, Ång</t>
+          <t>Kvarnbäcken Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>672862</v>
+        <v>672842</v>
       </c>
       <c r="R55" t="n">
-        <v>7090889</v>
+        <v>7090847</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6006,12 +5965,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
@@ -6022,14 +5981,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126919060</v>
+        <v>126917438</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6051,19 +6010,22 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>672791</v>
+        <v>672721</v>
       </c>
       <c r="R56" t="n">
-        <v>7091150</v>
+        <v>7091214</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6101,18 +6063,19 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -6123,14 +6086,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126912879</v>
+        <v>126917439</v>
       </c>
       <c r="B57" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6152,19 +6115,22 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>672751</v>
+        <v>672721</v>
       </c>
       <c r="R57" t="n">
-        <v>7091095</v>
+        <v>7091190</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6196,38 +6162,48 @@
           <t>2025-07-25</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126912868</v>
+        <v>126917440</v>
       </c>
       <c r="B58" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6249,19 +6225,22 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>672779</v>
+        <v>672718</v>
       </c>
       <c r="R58" t="n">
-        <v>7091147</v>
+        <v>7091186</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6299,66 +6278,74 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY58" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126919018</v>
+        <v>126917441</v>
       </c>
       <c r="B59" t="n">
-        <v>56855</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>672883</v>
+        <v>672705</v>
       </c>
       <c r="R59" t="n">
-        <v>7090877</v>
+        <v>7091153</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6390,29 +6377,25 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Spillning färsk</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
@@ -6423,48 +6406,51 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126912934</v>
+        <v>126917442</v>
       </c>
       <c r="B60" t="n">
-        <v>78687</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>672873</v>
+        <v>672706</v>
       </c>
       <c r="R60" t="n">
-        <v>7090916</v>
+        <v>7091137</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6502,66 +6488,74 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126913217</v>
+        <v>126917443</v>
       </c>
       <c r="B61" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>672643</v>
+        <v>672714</v>
       </c>
       <c r="R61" t="n">
-        <v>7091013</v>
+        <v>7091092</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6599,18 +6593,19 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr">
@@ -6621,14 +6616,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126912884</v>
+        <v>126917444</v>
       </c>
       <c r="B62" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6650,19 +6645,22 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>672746</v>
+        <v>672729</v>
       </c>
       <c r="R62" t="n">
-        <v>7091051</v>
+        <v>7091024</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6700,32 +6698,37 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126912892</v>
+        <v>126917445</v>
       </c>
       <c r="B63" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6747,19 +6750,22 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>672787</v>
+        <v>672706</v>
       </c>
       <c r="R63" t="n">
-        <v>7090995</v>
+        <v>7090986</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6797,50 +6803,55 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Roger Adolfsson, Alexandra Astafourova, Lars-Erik Nilsson, Martin Axegård, Vilhelm Kroon, Alva Danielsson, Liam Sebestyén, Cajsa Björkén, Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126917430</v>
+        <v>126917446</v>
       </c>
       <c r="B64" t="n">
-        <v>79052</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6853,10 +6864,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>672707</v>
+        <v>672779</v>
       </c>
       <c r="R64" t="n">
-        <v>7091108</v>
+        <v>7090893</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6920,14 +6931,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126917438</v>
+        <v>126918816</v>
       </c>
       <c r="B65" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -6949,22 +6960,19 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>672721</v>
+        <v>672813</v>
       </c>
       <c r="R65" t="n">
-        <v>7091214</v>
+        <v>7091072</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7002,19 +7010,18 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
@@ -7025,14 +7032,14 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126917439</v>
+        <v>126918818</v>
       </c>
       <c r="B66" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7054,22 +7061,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>672721</v>
+        <v>672802</v>
       </c>
       <c r="R66" t="n">
-        <v>7091190</v>
+        <v>7091202</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7101,30 +7105,24 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
@@ -7135,14 +7133,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126917445</v>
+        <v>126918819</v>
       </c>
       <c r="B67" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7164,22 +7162,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>672706</v>
+        <v>672815</v>
       </c>
       <c r="R67" t="n">
-        <v>7090986</v>
+        <v>7091165</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7217,19 +7212,18 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -7240,52 +7234,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126917433</v>
+        <v>126918820</v>
       </c>
       <c r="B68" t="n">
-        <v>56855</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>672876</v>
+        <v>672755</v>
       </c>
       <c r="R68" t="n">
-        <v>7090878</v>
+        <v>7091121</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7315,11 +7305,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>30 krokar under tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7334,12 +7319,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -7350,51 +7335,48 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126917436</v>
+        <v>126918821</v>
       </c>
       <c r="B69" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>672884</v>
+        <v>672752</v>
       </c>
       <c r="R69" t="n">
-        <v>7090863</v>
+        <v>7091197</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7432,19 +7414,18 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
@@ -7455,14 +7436,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126917440</v>
+        <v>126918823</v>
       </c>
       <c r="B70" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7484,22 +7465,19 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>672718</v>
+        <v>672788</v>
       </c>
       <c r="R70" t="n">
         <v>7091186</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7537,19 +7515,18 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -7560,14 +7537,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126917441</v>
+        <v>126918824</v>
       </c>
       <c r="B71" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7589,22 +7566,19 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>672705</v>
+        <v>672781</v>
       </c>
       <c r="R71" t="n">
-        <v>7091153</v>
+        <v>7091162</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7642,19 +7616,18 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr">
@@ -7665,56 +7638,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126917434</v>
+        <v>126918825</v>
       </c>
       <c r="B72" t="n">
-        <v>57823</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>672734</v>
+        <v>672764</v>
       </c>
       <c r="R72" t="n">
-        <v>7091231</v>
+        <v>7091153</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7758,12 +7723,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -7774,14 +7739,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126917444</v>
+        <v>126918826</v>
       </c>
       <c r="B73" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7803,22 +7768,19 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>672729</v>
+        <v>672744</v>
       </c>
       <c r="R73" t="n">
-        <v>7091024</v>
+        <v>7091079</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7856,19 +7818,18 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
@@ -7879,14 +7840,14 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126917442</v>
+        <v>126918827</v>
       </c>
       <c r="B74" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -7908,22 +7869,19 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>672706</v>
+        <v>672753</v>
       </c>
       <c r="R74" t="n">
-        <v>7091137</v>
+        <v>7091016</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7961,19 +7919,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -7984,10 +7941,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126917447</v>
+        <v>126918828</v>
       </c>
       <c r="B75" t="n">
-        <v>91593</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7995,40 +7952,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>65</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>672713</v>
+        <v>672757</v>
       </c>
       <c r="R75" t="n">
-        <v>7090990</v>
+        <v>7091027</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8066,19 +8020,18 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -8089,14 +8042,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126917443</v>
+        <v>126918830</v>
       </c>
       <c r="B76" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8118,22 +8071,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>672714</v>
+        <v>672770</v>
       </c>
       <c r="R76" t="n">
-        <v>7091092</v>
+        <v>7090981</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8171,19 +8121,18 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
@@ -8194,52 +8143,48 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126917432</v>
+        <v>126918831</v>
       </c>
       <c r="B77" t="n">
-        <v>56855</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>672737</v>
+        <v>672756</v>
       </c>
       <c r="R77" t="n">
-        <v>7091034</v>
+        <v>7090952</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8269,11 +8214,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-07-25</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Spillningshög under gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8288,12 +8228,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
@@ -8304,45 +8244,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126913591</v>
+        <v>126918832</v>
       </c>
       <c r="B78" t="n">
-        <v>78687</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>672892</v>
+        <v>672794</v>
       </c>
       <c r="R78" t="n">
-        <v>7090833</v>
+        <v>7090881</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8389,12 +8329,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -8405,45 +8345,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126913592</v>
+        <v>126919048</v>
       </c>
       <c r="B79" t="n">
-        <v>79638</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>672892</v>
+        <v>672629</v>
       </c>
       <c r="R79" t="n">
-        <v>7090833</v>
+        <v>7091025</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8490,12 +8430,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -8506,14 +8446,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126913583</v>
+        <v>126919049</v>
       </c>
       <c r="B80" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8537,14 +8477,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>672728</v>
+        <v>672651</v>
       </c>
       <c r="R80" t="n">
-        <v>7091029</v>
+        <v>7091012</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8591,12 +8531,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
@@ -8607,45 +8547,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126913586</v>
+        <v>126919050</v>
       </c>
       <c r="B81" t="n">
-        <v>78779</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>672891</v>
+        <v>672719</v>
       </c>
       <c r="R81" t="n">
-        <v>7090896</v>
+        <v>7091052</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8692,12 +8632,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
@@ -8708,45 +8648,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126913587</v>
+        <v>126919051</v>
       </c>
       <c r="B82" t="n">
-        <v>79609</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>672940</v>
+        <v>672702</v>
       </c>
       <c r="R82" t="n">
-        <v>7090870</v>
+        <v>7091061</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8793,12 +8733,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
@@ -8809,45 +8749,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126913589</v>
+        <v>126919053</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>672864</v>
+        <v>672698</v>
       </c>
       <c r="R83" t="n">
-        <v>7090849</v>
+        <v>7091075</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8894,12 +8834,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
@@ -8910,45 +8850,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126913588</v>
+        <v>126919054</v>
       </c>
       <c r="B84" t="n">
-        <v>79052</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>672865</v>
+        <v>672705</v>
       </c>
       <c r="R84" t="n">
-        <v>7090849</v>
+        <v>7091127</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8995,12 +8935,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
@@ -9011,14 +8951,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126913582</v>
+        <v>126919056</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -9042,14 +8982,14 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>672738</v>
+        <v>672702</v>
       </c>
       <c r="R85" t="n">
-        <v>7091189</v>
+        <v>7091127</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9096,12 +9036,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
@@ -9112,14 +9052,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126913584</v>
+        <v>126919057</v>
       </c>
       <c r="B86" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -9143,14 +9083,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>672813</v>
+        <v>672730</v>
       </c>
       <c r="R86" t="n">
-        <v>7091003</v>
+        <v>7091091</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9197,12 +9137,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
@@ -9213,14 +9153,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126913585</v>
+        <v>126919058</v>
       </c>
       <c r="B87" t="n">
-        <v>79020</v>
+        <v>79327</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -9244,14 +9184,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>672813</v>
+        <v>672737</v>
       </c>
       <c r="R87" t="n">
-        <v>7090992</v>
+        <v>7091090</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9298,12 +9238,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Roger Adolfsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -9314,45 +9254,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126913593</v>
+        <v>126919059</v>
       </c>
       <c r="B88" t="n">
-        <v>79052</v>
+        <v>79327</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Kvarnbäcken Lappberget, Ång</t>
+          <t>Lappberget, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>672910</v>
+        <v>672732</v>
       </c>
       <c r="R88" t="n">
-        <v>7090821</v>
+        <v>7091173</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9399,15 +9339,2650 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>126919060</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>672791</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7091150</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>126913589</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79351</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Kvarnbäcken Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>672864</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7090849</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
+      <c r="AX90" t="inlineStr">
         <is>
           <t>Cajsa Björkén</t>
         </is>
       </c>
-      <c r="AY88" t="inlineStr">
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>126912944</v>
+      </c>
+      <c r="B91" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>672756</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7091093</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>På torraka med 4 brandljud</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>126913221</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>672646</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7090962</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126912724</v>
+      </c>
+      <c r="B93" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>672801</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7091211</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>126918815</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>672767</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7090991</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>126912713</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>672780</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7091043</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>126912715</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>672914</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7090807</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>126912716</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>672745</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7091092</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>126912717</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>672735</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7091083</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>126912718</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>672824</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7090912</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>126913217</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>672643</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7091013</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>126913592</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Kvarnbäcken Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>672892</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7090833</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>126918813</v>
+      </c>
+      <c r="B102" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>672808</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7091191</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Cajsa Björkén, Liam Sebestyén, Martin Axegård, Alexandra Astafourova, Lars-Erik Nilsson, Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>126913222</v>
+      </c>
+      <c r="B103" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>672883</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7090921</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>126917432</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>672737</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7091034</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Spillningshög under gran</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>126917433</v>
+      </c>
+      <c r="B105" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>672876</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7090878</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>30 krokar under tall</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>126919018</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>672883</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7090877</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Spillning färsk</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>126919016</v>
+      </c>
+      <c r="B107" t="n">
+        <v>57774</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>102976</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Tornseglare</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Apus apus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>672887</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7090802</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>126917434</v>
+      </c>
+      <c r="B108" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>672734</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7091231</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>126912743</v>
+      </c>
+      <c r="B109" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>672864</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7090784</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>126913220</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>672644</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7090962</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén, Philipp Weiss, Cajsa Björkén, Martin Axegård, Alexandra Astafourova, Alva Danielsson, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>126913586</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Kvarnbäcken Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>672891</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7090896</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>126917436</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>672884</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7090863</v>
+      </c>
+      <c r="S112" t="n">
+        <v>15</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon, Roger Adolfsson, Alexandra Astafourova, Cajsa Björkén, Philipp Weiss, Alva Danielsson, Martin Axegård, Liam Sebestyén, Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>126912726</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>672750</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7091112</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Philipp Weiss, Cajsa Björkén, Liam Sebestyén, Alva Danielsson, Vilhelm Kroon, Martin Axegård, Lars-Erik Nilsson, Alexandra Astafourova, Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>126913587</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Kvarnbäcken Lappberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>672940</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7090870</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Bjurholm</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>

--- a/artfynd/A 46978-2024 artfynd.xlsx
+++ b/artfynd/A 46978-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY114"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913218</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913219</t>
         </is>
       </c>
     </row>
@@ -979,6 +994,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917441</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917442</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917445</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919048</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919049</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1492,6 +1532,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919051</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919053</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919054</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1795,6 +1850,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919056</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913221</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1997,6 +2062,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913217</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
       <c r="AY15" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913220</t>
         </is>
       </c>
     </row>
@@ -2203,6 +2278,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917447</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2300,6 +2380,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912725</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913223</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2502,6 +2592,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913588</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2601,6 +2696,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913593</t>
         </is>
       </c>
     </row>
@@ -2708,6 +2808,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2805,6 +2910,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912930</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2902,6 +3012,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912931</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2999,6 +3114,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912932</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3193,6 +3318,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3290,6 +3420,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912935</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3391,6 +3526,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913591</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3488,6 +3628,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912749</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3585,6 +3730,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912723</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3682,6 +3832,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912927</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3779,6 +3934,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912928</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3880,6 +4040,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919079</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3977,6 +4142,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80865059</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4074,6 +4244,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912774</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4171,6 +4346,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912776</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4268,6 +4448,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912840</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4365,6 +4550,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912844</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4462,6 +4652,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912847</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4559,6 +4754,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912851</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4656,6 +4856,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912853</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4753,6 +4958,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912855</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4850,6 +5060,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912858</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4947,6 +5162,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912860</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5044,6 +5264,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912862</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5141,6 +5366,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912865</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5238,6 +5468,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912868</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5335,6 +5570,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912870</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5432,6 +5672,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912873</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5529,6 +5774,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912875</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5626,6 +5876,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912877</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5723,6 +5978,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912879</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5820,6 +6080,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912882</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5917,6 +6182,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912884</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6014,6 +6284,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912887</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6111,6 +6386,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912889</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6208,6 +6488,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912892</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6305,6 +6590,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912894</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6402,6 +6692,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912898</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6499,6 +6794,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912901</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6596,6 +6896,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912903</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6697,6 +7002,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913216</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6798,6 +7108,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913582</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6899,6 +7214,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913583</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7000,6 +7320,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913584</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7101,6 +7426,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913585</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7200,6 +7530,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913590</t>
         </is>
       </c>
     </row>
@@ -7307,6 +7642,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917438</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7417,6 +7757,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917439</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7522,6 +7867,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917440</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7627,6 +7977,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917443</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7732,6 +8087,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917444</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7837,6 +8197,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917446</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7938,6 +8303,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918816</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8039,6 +8409,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918818</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8140,6 +8515,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918819</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8241,6 +8621,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918820</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8342,6 +8727,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918821</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8443,6 +8833,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918823</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8544,6 +8939,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918824</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8645,6 +9045,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918825</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8746,6 +9151,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918826</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8847,6 +9257,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918827</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8948,6 +9363,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918828</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9049,6 +9469,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918830</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9150,6 +9575,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918831</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9251,6 +9681,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918832</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9352,6 +9787,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919050</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9453,6 +9893,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919057</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9554,6 +9999,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919058</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9655,6 +10105,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919059</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9756,6 +10211,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919060</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9857,6 +10317,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913589</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9959,6 +10424,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912944</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10056,6 +10526,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912724</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10157,6 +10632,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918815</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10254,6 +10734,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912713</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10351,6 +10836,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912715</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10448,6 +10938,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912716</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10545,6 +11040,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912717</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10642,6 +11142,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912718</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10743,6 +11248,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913592</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10849,6 +11359,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126918813</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10948,6 +11463,11 @@
       <c r="AY104" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913222</t>
         </is>
       </c>
     </row>
@@ -11060,6 +11580,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917432</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11170,6 +11695,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917433</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11276,6 +11806,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919018</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11377,6 +11912,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126919016</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11486,6 +12026,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917434</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11583,6 +12128,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912743</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11682,6 +12232,11 @@
       <c r="AY111" t="inlineStr">
         <is>
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913586</t>
         </is>
       </c>
     </row>
@@ -11789,6 +12344,11 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126917436</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11886,6 +12446,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126912726</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11987,8 +12552,128 @@
           <t>Forskningsresan i naturvårdens utmarker, Bjurholm 2025</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126913587</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>